--- a/data/업로드양식_원료단가사용.xlsx
+++ b/data/업로드양식_원료단가사용.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\원료비원인분석\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\업무\36. 개발노트\원료비원인분석\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E156540-3119-4638-B102-74C5FF979A6C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17BB63F-30E4-4B55-99E0-AB98C52D1CFE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3301" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3815" uniqueCount="391">
   <si>
     <t>년월</t>
   </si>
@@ -1197,6 +1197,10 @@
   </si>
   <si>
     <t>2026-06</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-07</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1604,11 +1608,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1543"/>
+  <dimension ref="A1:F1800"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="27.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -34010,6 +34015,3604 @@
       </c>
       <c r="F1543" s="3">
         <f t="shared" ref="F1543" si="24">E1543*D1543</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1544" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1544" s="2">
+        <v>1010101</v>
+      </c>
+      <c r="C1544" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1544" s="3">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1545" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1545" s="2">
+        <v>1010111</v>
+      </c>
+      <c r="C1545" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1545" s="3">
+        <v>19100</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1546" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1546" s="2">
+        <v>1010201</v>
+      </c>
+      <c r="C1546" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1546" s="3">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1547" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1547" s="2">
+        <v>1010300</v>
+      </c>
+      <c r="C1547" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1547" s="3">
+        <v>9608</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1548" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1548" s="2">
+        <v>1010301</v>
+      </c>
+      <c r="C1548" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1548" s="3">
+        <v>6373</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1549" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1549" s="2">
+        <v>1010302</v>
+      </c>
+      <c r="C1549" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1549" s="3">
+        <v>4314</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1550" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1550" s="2">
+        <v>1010303</v>
+      </c>
+      <c r="C1550" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1550" s="3">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1551" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1551" s="2">
+        <v>1010304</v>
+      </c>
+      <c r="C1551" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1551" s="3">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1552" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1552" s="2">
+        <v>1010401</v>
+      </c>
+      <c r="C1552" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1552" s="3">
+        <v>3627</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1553" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1553" s="2">
+        <v>1010405</v>
+      </c>
+      <c r="C1553" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1553" s="3">
+        <v>9975</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1554" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1554" s="2">
+        <v>1010501</v>
+      </c>
+      <c r="C1554" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1554" s="3">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1555" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1555" s="2">
+        <v>1010502</v>
+      </c>
+      <c r="C1555" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1555" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1556" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1556" s="2">
+        <v>1010601</v>
+      </c>
+      <c r="C1556" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1556" s="3">
+        <v>4902</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1557" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1557" s="2">
+        <v>1010701</v>
+      </c>
+      <c r="C1557" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1557" s="3">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1558" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1558" s="2">
+        <v>1010801</v>
+      </c>
+      <c r="C1558" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1558" s="3">
+        <v>9449</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1559" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1559" s="2">
+        <v>1010901</v>
+      </c>
+      <c r="C1559" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1559" s="3">
+        <v>4804</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1560" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1560" s="2">
+        <v>1020101</v>
+      </c>
+      <c r="C1560" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1560" s="3">
+        <v>11667</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1561" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1561" s="2">
+        <v>1020201</v>
+      </c>
+      <c r="C1561" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1561" s="3">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1562" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1562" s="2">
+        <v>1020301</v>
+      </c>
+      <c r="C1562" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1562" s="3">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1563" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1563" s="2">
+        <v>1020401</v>
+      </c>
+      <c r="C1563" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1563" s="3">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1564" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1564" s="2">
+        <v>1030102</v>
+      </c>
+      <c r="C1564" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D1564" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1565" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1565" s="2">
+        <v>1030201</v>
+      </c>
+      <c r="C1565" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1565" s="3">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1566" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1566" s="2">
+        <v>1030203</v>
+      </c>
+      <c r="C1566" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1566" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1567" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1567" s="2">
+        <v>1030204</v>
+      </c>
+      <c r="C1567" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1567" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1568" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1568" s="2">
+        <v>1030205</v>
+      </c>
+      <c r="C1568" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1568" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1569" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1569" s="2">
+        <v>1030206</v>
+      </c>
+      <c r="C1569" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1569" s="3">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1570" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1570" s="2">
+        <v>1030207</v>
+      </c>
+      <c r="C1570" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1570" s="3">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1571" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1571" s="2">
+        <v>1030501</v>
+      </c>
+      <c r="C1571" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1571" s="3">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1572" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1572" s="2">
+        <v>1030601</v>
+      </c>
+      <c r="C1572" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1572" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1573" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1573" s="2">
+        <v>1030701</v>
+      </c>
+      <c r="C1573" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1573" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1574" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1574" s="2">
+        <v>1030705</v>
+      </c>
+      <c r="C1574" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1574" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1575" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1575" s="2">
+        <v>1030801</v>
+      </c>
+      <c r="C1575" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1575" s="3">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1576" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1576" s="2">
+        <v>1030901</v>
+      </c>
+      <c r="C1576" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1576" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1577" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1577" s="2">
+        <v>1040201</v>
+      </c>
+      <c r="C1577" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1577" s="3">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1578" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1578" s="2">
+        <v>1040202</v>
+      </c>
+      <c r="C1578" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1578" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1579" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1579" s="2">
+        <v>1040203</v>
+      </c>
+      <c r="C1579" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1579" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1580" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1580" s="2">
+        <v>1040204</v>
+      </c>
+      <c r="C1580" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D1580" s="3">
+        <v>8583</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1581" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1581" s="2">
+        <v>1040301</v>
+      </c>
+      <c r="C1581" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1581" s="3">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1582" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1582" s="2">
+        <v>1040401</v>
+      </c>
+      <c r="C1582" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1582" s="3">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1583" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1583" s="2">
+        <v>1050102</v>
+      </c>
+      <c r="C1583" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1583" s="3">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1584" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1584" s="2">
+        <v>1050103</v>
+      </c>
+      <c r="C1584" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D1584" s="3">
+        <v>11275</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1585" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1585" s="2">
+        <v>1050301</v>
+      </c>
+      <c r="C1585" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1585" s="3">
+        <v>9804</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1586" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1586" s="2">
+        <v>1050401</v>
+      </c>
+      <c r="C1586" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1586" s="3">
+        <v>8824</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1587" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1587" s="2">
+        <v>1050501</v>
+      </c>
+      <c r="C1587" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1587" s="3">
+        <v>10784</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1588" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1588" s="2">
+        <v>1050511</v>
+      </c>
+      <c r="C1588" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1588" s="3">
+        <v>17647</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1589" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1589" s="2">
+        <v>1050512</v>
+      </c>
+      <c r="C1589" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1589" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1590" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1590" s="2">
+        <v>1050521</v>
+      </c>
+      <c r="C1590" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1590" s="3">
+        <v>14706</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1591" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1591" s="2">
+        <v>1050531</v>
+      </c>
+      <c r="C1591" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1591" s="3">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1592" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1592" s="2">
+        <v>1050541</v>
+      </c>
+      <c r="C1592" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1592" s="3">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1593" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1593" s="2">
+        <v>1050551</v>
+      </c>
+      <c r="C1593" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1593" s="3">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1594" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1594" s="2">
+        <v>1050561</v>
+      </c>
+      <c r="C1594" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1594" s="3">
+        <v>77321</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1595" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1595" s="2">
+        <v>1050571</v>
+      </c>
+      <c r="C1595" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1595" s="3">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1596" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1596" s="2">
+        <v>1050581</v>
+      </c>
+      <c r="C1596" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1596" s="3">
+        <v>60760</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1597" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1597" s="2">
+        <v>1050591</v>
+      </c>
+      <c r="C1597" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1597" s="3">
+        <v>97750</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1598" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1598" s="2">
+        <v>1050601</v>
+      </c>
+      <c r="C1598" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1598" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1599" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1599" s="2">
+        <v>1050701</v>
+      </c>
+      <c r="C1599" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1599" s="3">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1600" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1600" s="2">
+        <v>1050702</v>
+      </c>
+      <c r="C1600" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1600" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1601" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1601" s="2">
+        <v>1050711</v>
+      </c>
+      <c r="C1601" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1601" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1602" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1602" s="2">
+        <v>1050721</v>
+      </c>
+      <c r="C1602" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1602" s="3">
+        <v>14510</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1603" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1603" s="2">
+        <v>1050801</v>
+      </c>
+      <c r="C1603" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1603" s="3">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1604" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1604" s="2">
+        <v>1050901</v>
+      </c>
+      <c r="C1604" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1604" s="3">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1605" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1605" s="2">
+        <v>1060101</v>
+      </c>
+      <c r="C1605" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1605" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1606" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1606" s="2">
+        <v>1060401</v>
+      </c>
+      <c r="C1606" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1606" s="3">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1607" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1607" s="2">
+        <v>1060412</v>
+      </c>
+      <c r="C1607" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D1607" s="3">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1608" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1608" s="2">
+        <v>1060421</v>
+      </c>
+      <c r="C1608" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1608" s="3">
+        <v>118000</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1609" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1609" s="2">
+        <v>1060441</v>
+      </c>
+      <c r="C1609" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1609" s="3">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1610" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1610" s="2">
+        <v>1060451</v>
+      </c>
+      <c r="C1610" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1610" s="3">
+        <v>38235</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1611" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1611" s="2">
+        <v>1070101</v>
+      </c>
+      <c r="C1611" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1611" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1612" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1612" s="2">
+        <v>1070301</v>
+      </c>
+      <c r="C1612" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1612" s="3">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1613" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1613" s="2">
+        <v>1070401</v>
+      </c>
+      <c r="C1613" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1613" s="3">
+        <v>15478</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1614" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1614" s="2">
+        <v>1070501</v>
+      </c>
+      <c r="C1614" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1614" s="3">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1615" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1615" s="2">
+        <v>1070701</v>
+      </c>
+      <c r="C1615" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1615" s="3">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1616" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1616" s="2">
+        <v>1070801</v>
+      </c>
+      <c r="C1616" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1616" s="3">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1617" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1617" s="2">
+        <v>1080101</v>
+      </c>
+      <c r="C1617" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1617" s="3">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1618" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1618" s="2">
+        <v>1080201</v>
+      </c>
+      <c r="C1618" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1618" s="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1619" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1619" s="2">
+        <v>1080301</v>
+      </c>
+      <c r="C1619" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1619" s="3">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1620" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1620" s="2">
+        <v>1080401</v>
+      </c>
+      <c r="C1620" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1620" s="3">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1621" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1621" s="2">
+        <v>1080411</v>
+      </c>
+      <c r="C1621" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1621" s="3">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1622" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1622" s="2">
+        <v>1080501</v>
+      </c>
+      <c r="C1622" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1622" s="3">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1623" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1623" s="2">
+        <v>1080602</v>
+      </c>
+      <c r="C1623" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1623" s="3">
+        <v>38600</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1624" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1624" s="2">
+        <v>1080604</v>
+      </c>
+      <c r="C1624" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1624" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1625" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1625" s="2">
+        <v>1080702</v>
+      </c>
+      <c r="C1625" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1625" s="3">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1626" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1626" s="2">
+        <v>1080704</v>
+      </c>
+      <c r="C1626" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1626" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1627" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1627" s="2">
+        <v>1090104</v>
+      </c>
+      <c r="C1627" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1627" s="3">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1628" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1628" s="2">
+        <v>1090112</v>
+      </c>
+      <c r="C1628" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1628" s="3">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1629" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1629" s="2">
+        <v>1090201</v>
+      </c>
+      <c r="C1629" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1629" s="3">
+        <v>15800</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1630" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1630" s="2">
+        <v>1090202</v>
+      </c>
+      <c r="C1630" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1630" s="3">
+        <v>98000</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1631" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1631" s="2">
+        <v>1090203</v>
+      </c>
+      <c r="C1631" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1631" s="3">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1632" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1632" s="2">
+        <v>1090211</v>
+      </c>
+      <c r="C1632" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1632" s="3">
+        <v>64706</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1633" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1633" s="2">
+        <v>1090301</v>
+      </c>
+      <c r="C1633" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1633" s="3">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1634" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1634" s="2">
+        <v>1090311</v>
+      </c>
+      <c r="C1634" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1634" s="3">
+        <v>37000</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1635" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1635" s="2">
+        <v>1090321</v>
+      </c>
+      <c r="C1635" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1635" s="3">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1636" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1636" s="2">
+        <v>1090401</v>
+      </c>
+      <c r="C1636" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1636" s="3">
+        <v>9300</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1637" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1637" s="2">
+        <v>1090411</v>
+      </c>
+      <c r="C1637" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1637" s="3">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1638" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1638" s="2">
+        <v>1090421</v>
+      </c>
+      <c r="C1638" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1638" s="3">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1639" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1639" s="2">
+        <v>1090551</v>
+      </c>
+      <c r="C1639" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D1639" s="3">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1640" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1640" s="2">
+        <v>1090602</v>
+      </c>
+      <c r="C1640" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1640" s="3">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1641" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1641" s="2">
+        <v>1090611</v>
+      </c>
+      <c r="C1641" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1641" s="3">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1642" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1642" s="2">
+        <v>1090701</v>
+      </c>
+      <c r="C1642" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1642" s="3">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1643" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1643" s="2">
+        <v>1090901</v>
+      </c>
+      <c r="C1643" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1643" s="3">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1644" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1644" s="2">
+        <v>1091001</v>
+      </c>
+      <c r="C1644" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1644" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1645" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1645" s="2">
+        <v>1091002</v>
+      </c>
+      <c r="C1645" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1645" s="3">
+        <v>4402</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1646" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1646" s="2">
+        <v>1091003</v>
+      </c>
+      <c r="C1646" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1646" s="3">
+        <v>14014</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1647" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1647" s="2">
+        <v>1091004</v>
+      </c>
+      <c r="C1647" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D1647" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1648" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1648" s="2">
+        <v>1091005</v>
+      </c>
+      <c r="C1648" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D1648" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1649" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1649" s="2">
+        <v>1091006</v>
+      </c>
+      <c r="C1649" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1649" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1650" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1650" s="2">
+        <v>1091007</v>
+      </c>
+      <c r="C1650" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D1650" s="3">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1651" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1651" s="2">
+        <v>1091008</v>
+      </c>
+      <c r="C1651" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D1651" s="3">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1652" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1652" s="2">
+        <v>1091009</v>
+      </c>
+      <c r="C1652" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1652" s="3">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1653" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1653" s="2">
+        <v>1091010</v>
+      </c>
+      <c r="C1653" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1653" s="3">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1654" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1654" s="2">
+        <v>1091011</v>
+      </c>
+      <c r="C1654" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1654" s="3">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1655" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1655" s="2">
+        <v>1091012</v>
+      </c>
+      <c r="C1655" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1655" s="3">
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1656" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1656" s="2">
+        <v>1091013</v>
+      </c>
+      <c r="C1656" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1656" s="3">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1657" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1657" s="2">
+        <v>1091014</v>
+      </c>
+      <c r="C1657" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1657" s="3">
+        <v>6961</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1658" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1658" s="2">
+        <v>1091015</v>
+      </c>
+      <c r="C1658" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D1658" s="3">
+        <v>25490</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1659" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1659" s="2">
+        <v>1091016</v>
+      </c>
+      <c r="C1659" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D1659" s="3">
+        <v>50187</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1660" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1660" s="2">
+        <v>1091017</v>
+      </c>
+      <c r="C1660" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1660" s="3">
+        <v>74833</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1661" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1661" s="2">
+        <v>1091018</v>
+      </c>
+      <c r="C1661" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1661" s="3">
+        <v>33031</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1662" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1662" s="2">
+        <v>1091019</v>
+      </c>
+      <c r="C1662" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1662" s="3">
+        <v>53387</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1663" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1663" s="2">
+        <v>1091020</v>
+      </c>
+      <c r="C1663" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1663" s="3">
+        <v>100500</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1664" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1664" s="2">
+        <v>1091021</v>
+      </c>
+      <c r="C1664" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1664" s="3">
+        <v>50600</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1665" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1665" s="2">
+        <v>1091022</v>
+      </c>
+      <c r="C1665" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D1665" s="3">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1666" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1666" s="2">
+        <v>1091023</v>
+      </c>
+      <c r="C1666" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1666" s="3">
+        <v>4412</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1667" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1667" s="2">
+        <v>1091024</v>
+      </c>
+      <c r="C1667" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1667" s="3">
+        <v>3922</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1668" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1668" s="2">
+        <v>1091025</v>
+      </c>
+      <c r="C1668" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1668" s="3">
+        <v>7843</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1669" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1669" s="2">
+        <v>1091026</v>
+      </c>
+      <c r="C1669" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1669" s="3">
+        <v>30686</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1670" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1670" s="2">
+        <v>1600101</v>
+      </c>
+      <c r="C1670" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D1670" s="3">
+        <v>2892</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1671" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1671" s="2">
+        <v>1600102</v>
+      </c>
+      <c r="C1671" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D1671" s="3">
+        <v>26962</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1672" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1672" s="2">
+        <v>1600103</v>
+      </c>
+      <c r="C1672" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1672" s="3">
+        <v>19800</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1673" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1673" s="2">
+        <v>1600104</v>
+      </c>
+      <c r="C1673" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D1673" s="3">
+        <v>75683</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1674" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1674" s="2">
+        <v>1600105</v>
+      </c>
+      <c r="C1674" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1674" s="3">
+        <v>83950</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1675" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1675" s="2">
+        <v>1600106</v>
+      </c>
+      <c r="C1675" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1675" s="3">
+        <v>108071</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1676" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1676" s="2">
+        <v>1600107</v>
+      </c>
+      <c r="C1676" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1676" s="3">
+        <v>86601</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1677" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1677" s="2">
+        <v>1600108</v>
+      </c>
+      <c r="C1677" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1677" s="3">
+        <v>75683</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1678" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1678" s="2">
+        <v>1600109</v>
+      </c>
+      <c r="C1678" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1678" s="3">
+        <v>3922</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1679" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1679" s="2">
+        <v>1600110</v>
+      </c>
+      <c r="C1679" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1679" s="3">
+        <v>7917</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1680" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1680" s="2">
+        <v>1600111</v>
+      </c>
+      <c r="C1680" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1680" s="3">
+        <v>4360</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1681" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1681" s="2">
+        <v>1600112</v>
+      </c>
+      <c r="C1681" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1681" s="3">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1682" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1682" s="2">
+        <v>1600113</v>
+      </c>
+      <c r="C1682" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1682" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1683" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1683" s="2">
+        <v>1600114</v>
+      </c>
+      <c r="C1683" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1683" s="3">
+        <v>13333</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1684" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1684" s="2">
+        <v>1700001</v>
+      </c>
+      <c r="C1684" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1684" s="3">
+        <v>5274</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1685" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1685" s="2">
+        <v>1700002</v>
+      </c>
+      <c r="C1685" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D1685" s="3">
+        <v>3726</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1686" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1686" s="2">
+        <v>1700003</v>
+      </c>
+      <c r="C1686" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1686" s="3">
+        <v>5098</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1687" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1687" s="2">
+        <v>1700004</v>
+      </c>
+      <c r="C1687" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1687" s="3">
+        <v>15784</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1688" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1688" s="2">
+        <v>1700005</v>
+      </c>
+      <c r="C1688" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1688" s="3">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1689" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1689" s="2">
+        <v>1700006</v>
+      </c>
+      <c r="C1689" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D1689" s="3">
+        <v>7176</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1690" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1690" s="2">
+        <v>1700007</v>
+      </c>
+      <c r="C1690" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D1690" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1691" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1691" s="2">
+        <v>1700008</v>
+      </c>
+      <c r="C1691" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D1691" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1692" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1692" s="2">
+        <v>1700009</v>
+      </c>
+      <c r="C1692" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D1692" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1693" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1693" s="2">
+        <v>1700010</v>
+      </c>
+      <c r="C1693" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D1693" s="3">
+        <v>4330</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1694" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1694" s="2">
+        <v>1700011</v>
+      </c>
+      <c r="C1694" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1694" s="3">
+        <v>13235</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1695" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1695" s="2">
+        <v>1700012</v>
+      </c>
+      <c r="C1695" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D1695" s="3">
+        <v>15980</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1696" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1696" s="2">
+        <v>1700013</v>
+      </c>
+      <c r="C1696" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1696" s="3">
+        <v>18137</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1697" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1697" s="2">
+        <v>1700014</v>
+      </c>
+      <c r="C1697" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D1697" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1698" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1698" s="2">
+        <v>1700015</v>
+      </c>
+      <c r="C1698" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1698" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1699" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1699" s="2">
+        <v>1700016</v>
+      </c>
+      <c r="C1699" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1699" s="3">
+        <v>4043</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1700" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1700" s="2">
+        <v>1700017</v>
+      </c>
+      <c r="C1700" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1700" s="3">
+        <v>12608</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1701" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1701" s="2">
+        <v>1700018</v>
+      </c>
+      <c r="C1701" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D1701" s="3">
+        <v>4472</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1702" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1702" s="2">
+        <v>1700019</v>
+      </c>
+      <c r="C1702" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1702" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1703" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1703" s="2">
+        <v>1700020</v>
+      </c>
+      <c r="C1703" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1703" s="3">
+        <v>58824</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1704" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1704" s="2">
+        <v>1700021</v>
+      </c>
+      <c r="C1704" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1704" s="3">
+        <v>90684</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1705" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1705" s="2">
+        <v>1700022</v>
+      </c>
+      <c r="C1705" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1705" s="3">
+        <v>35853</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1706" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1706" s="2">
+        <v>1700023</v>
+      </c>
+      <c r="C1706" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D1706" s="3">
+        <v>8136</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1707" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1707" s="2">
+        <v>1700024</v>
+      </c>
+      <c r="C1707" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D1707" s="3">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1708" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1708" s="2">
+        <v>1700025</v>
+      </c>
+      <c r="C1708" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D1708" s="3">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1709" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1709" s="2">
+        <v>1700026</v>
+      </c>
+      <c r="C1709" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1709" s="3">
+        <v>4412</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1710" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1710" s="2">
+        <v>1700027</v>
+      </c>
+      <c r="C1710" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D1710" s="3">
+        <v>4902</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1711" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1711" s="2">
+        <v>1700028</v>
+      </c>
+      <c r="C1711" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1711" s="3">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1712" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1712" s="2">
+        <v>1700029</v>
+      </c>
+      <c r="C1712" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1712" s="3">
+        <v>10670</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1713" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1713" s="2">
+        <v>1700030</v>
+      </c>
+      <c r="C1713" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D1713" s="3">
+        <v>12720</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1714" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1714" s="2">
+        <v>1700031</v>
+      </c>
+      <c r="C1714" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D1714" s="3">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1715" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1715" s="2">
+        <v>1700032</v>
+      </c>
+      <c r="C1715" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D1715" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1716" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1716" s="2">
+        <v>1700033</v>
+      </c>
+      <c r="C1716" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1716" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1717" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1717" s="2">
+        <v>1700034</v>
+      </c>
+      <c r="C1717" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1717" s="3">
+        <v>18700</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1718" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1718" s="2">
+        <v>1700035</v>
+      </c>
+      <c r="C1718" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D1718" s="3">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1719" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1719" s="2">
+        <v>1700036</v>
+      </c>
+      <c r="C1719" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D1719" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1720" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1720" s="2">
+        <v>1700037</v>
+      </c>
+      <c r="C1720" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D1720" s="3">
+        <v>7733</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1721" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1721" s="2">
+        <v>1700038</v>
+      </c>
+      <c r="C1721" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D1721" s="3">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1722" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1722" s="2">
+        <v>1700039</v>
+      </c>
+      <c r="C1722" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D1722" s="3">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1723" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1723" s="2">
+        <v>1700040</v>
+      </c>
+      <c r="C1723" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D1723" s="3">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1724" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1724" s="2">
+        <v>1700041</v>
+      </c>
+      <c r="C1724" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D1724" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1725" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1725" s="2">
+        <v>1700042</v>
+      </c>
+      <c r="C1725" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D1725" s="3">
+        <v>3402</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1726" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1726" s="2">
+        <v>1700043</v>
+      </c>
+      <c r="C1726" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D1726" s="3">
+        <v>6843</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1727" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1727" s="2">
+        <v>1700044</v>
+      </c>
+      <c r="C1727" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D1727" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1728" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1728" s="2">
+        <v>1700045</v>
+      </c>
+      <c r="C1728" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D1728" s="3">
+        <v>5265</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1729" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1729" s="2">
+        <v>1700046</v>
+      </c>
+      <c r="C1729" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D1729" s="3">
+        <v>6863</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1730" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1730" s="2">
+        <v>1700047</v>
+      </c>
+      <c r="C1730" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D1730" s="3">
+        <v>23800</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1731" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1731" s="2">
+        <v>1700048</v>
+      </c>
+      <c r="C1731" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D1731" s="3">
+        <v>13330</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1732" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1732" s="2">
+        <v>1700049</v>
+      </c>
+      <c r="C1732" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D1732" s="3">
+        <v>4062</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1733" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1733" s="2">
+        <v>1700050</v>
+      </c>
+      <c r="C1733" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D1733" s="3">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1734" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1734" s="2">
+        <v>1700051</v>
+      </c>
+      <c r="C1734" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D1734" s="3">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1735" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1735" s="2">
+        <v>1700052</v>
+      </c>
+      <c r="C1735" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D1735" s="3">
+        <v>3444</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1736" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1736" s="2">
+        <v>1700053</v>
+      </c>
+      <c r="C1736" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1736" s="3">
+        <v>15530</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1737" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1737" s="2">
+        <v>1700054</v>
+      </c>
+      <c r="C1737" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1737" s="3">
+        <v>11670</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1738" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1738" s="2">
+        <v>1700055</v>
+      </c>
+      <c r="C1738" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D1738" s="3">
+        <v>11940</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1739" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1739" s="2">
+        <v>1700056</v>
+      </c>
+      <c r="C1739" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D1739" s="3">
+        <v>6226</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1740" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1740" s="2">
+        <v>1700057</v>
+      </c>
+      <c r="C1740" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D1740" s="3">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1741" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1741" s="2">
+        <v>1700058</v>
+      </c>
+      <c r="C1741" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1741" s="3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1742" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1742" s="2">
+        <v>1700059</v>
+      </c>
+      <c r="C1742" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D1742" s="3">
+        <v>27667</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1743" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1743" s="2">
+        <v>1700060</v>
+      </c>
+      <c r="C1743" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D1743" s="3">
+        <v>3441</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1744" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1744" s="2">
+        <v>1700061</v>
+      </c>
+      <c r="C1744" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1744" s="3">
+        <v>8920</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1745" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1745" s="2">
+        <v>1700062</v>
+      </c>
+      <c r="C1745" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1745" s="3">
+        <v>10520</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1746" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1746" s="2">
+        <v>1700063</v>
+      </c>
+      <c r="C1746" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D1746" s="3">
+        <v>10550</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1747" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1747" s="2">
+        <v>1700064</v>
+      </c>
+      <c r="C1747" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D1747" s="3">
+        <v>11060</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1748" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1748" s="2">
+        <v>1700065</v>
+      </c>
+      <c r="C1748" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D1748" s="3">
+        <v>12760</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1749" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1749" s="2">
+        <v>1700066</v>
+      </c>
+      <c r="C1749" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D1749" s="3">
+        <v>13200</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1750" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1750" s="2">
+        <v>1700067</v>
+      </c>
+      <c r="C1750" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D1750" s="3">
+        <v>10720</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1751" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1751" s="2">
+        <v>1700068</v>
+      </c>
+      <c r="C1751" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D1751" s="3">
+        <v>12720</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1752" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1752" s="2">
+        <v>1700069</v>
+      </c>
+      <c r="C1752" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1752" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1753" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1753" s="2">
+        <v>1700070</v>
+      </c>
+      <c r="C1753" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D1753" s="3">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1754" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1754" s="2">
+        <v>1700071</v>
+      </c>
+      <c r="C1754" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1754" s="3">
+        <v>12190</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1755" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1755" s="2">
+        <v>1700072</v>
+      </c>
+      <c r="C1755" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D1755" s="3">
+        <v>10180</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1756" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1756" s="2">
+        <v>1700073</v>
+      </c>
+      <c r="C1756" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1756" s="3">
+        <v>9020</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1757" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1757" s="2">
+        <v>1700076</v>
+      </c>
+      <c r="C1757" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D1757" s="3">
+        <v>2693</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1758" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1758" s="2">
+        <v>1700077</v>
+      </c>
+      <c r="C1758" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D1758" s="3">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1759" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1759" s="2">
+        <v>1700078</v>
+      </c>
+      <c r="C1759" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D1759" s="3">
+        <v>4706</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1760" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1760" s="2">
+        <v>1700080</v>
+      </c>
+      <c r="C1760" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D1760" s="3">
+        <v>3922</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1761" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1761" s="2">
+        <v>1700083</v>
+      </c>
+      <c r="C1761" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1761" s="3">
+        <v>8333</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1762" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1762" s="2">
+        <v>1700084</v>
+      </c>
+      <c r="C1762" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D1762" s="3">
+        <v>6435</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1763" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1763" s="2">
+        <v>1700085</v>
+      </c>
+      <c r="C1763" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D1763" s="3">
+        <v>8720</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1764" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1764" s="2">
+        <v>1700086</v>
+      </c>
+      <c r="C1764" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D1764" s="3">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1765" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1765" s="2">
+        <v>1700087</v>
+      </c>
+      <c r="C1765" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D1765" s="3">
+        <v>4890</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1766" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1766" s="2">
+        <v>1700088</v>
+      </c>
+      <c r="C1766" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D1766" s="3">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1767" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1767" s="2">
+        <v>1700089</v>
+      </c>
+      <c r="C1767" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D1767" s="3">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1768" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1768" s="2">
+        <v>1700090</v>
+      </c>
+      <c r="C1768" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D1768" s="3">
+        <v>32843</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1769" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1769" s="2">
+        <v>1700091</v>
+      </c>
+      <c r="C1769" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1769" s="3">
+        <v>18353</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1770" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1770" s="2">
+        <v>1700092</v>
+      </c>
+      <c r="C1770" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D1770" s="3">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1771" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1771" s="2">
+        <v>1700093</v>
+      </c>
+      <c r="C1771" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D1771" s="3">
+        <v>12430</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1772" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1772" s="2">
+        <v>1700094</v>
+      </c>
+      <c r="C1772" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D1772" s="3">
+        <v>14020</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1773" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1773" s="2">
+        <v>1700095</v>
+      </c>
+      <c r="C1773" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D1773" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1774" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1774" s="2">
+        <v>1700096</v>
+      </c>
+      <c r="C1774" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D1774" s="3">
+        <v>24510</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1775" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1775" s="2">
+        <v>1700097</v>
+      </c>
+      <c r="C1775" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D1775" s="3">
+        <v>19608</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1776" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1776" s="2">
+        <v>1700098</v>
+      </c>
+      <c r="C1776" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1776" s="3">
+        <v>19608</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1777" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1777" s="2">
+        <v>1700099</v>
+      </c>
+      <c r="C1777" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D1777" s="3">
+        <v>9833</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1778" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1778" s="2">
+        <v>1700100</v>
+      </c>
+      <c r="C1778" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D1778" s="3">
+        <v>4220</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1779" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1779" s="2">
+        <v>1700101</v>
+      </c>
+      <c r="C1779" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D1779" s="3">
+        <v>7647</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1780" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1780" s="2">
+        <v>1700102</v>
+      </c>
+      <c r="C1780" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1780" s="3">
+        <v>40196</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1781" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1781" s="2">
+        <v>1700103</v>
+      </c>
+      <c r="C1781" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D1781" s="3">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1782" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1782" s="2">
+        <v>1700104</v>
+      </c>
+      <c r="C1782" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1782" s="3">
+        <v>25820</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1783" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1783" s="2">
+        <v>1700105</v>
+      </c>
+      <c r="C1783" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D1783" s="3">
+        <v>10588</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1784" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1784" s="2">
+        <v>1700106</v>
+      </c>
+      <c r="C1784" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D1784" s="3">
+        <v>14020</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1785" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1785" s="2">
+        <v>1700107</v>
+      </c>
+      <c r="C1785" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D1785" s="3">
+        <v>9020</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1786" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1786" s="2">
+        <v>1800002</v>
+      </c>
+      <c r="C1786" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1786" s="3">
+        <v>9520</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1787" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1787" s="2">
+        <v>1800004</v>
+      </c>
+      <c r="C1787" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D1787" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1788" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1788" s="2">
+        <v>1800005</v>
+      </c>
+      <c r="C1788" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1788" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1789" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1789" s="2">
+        <v>1800006</v>
+      </c>
+      <c r="C1789" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1789" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1790" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1790" s="2">
+        <v>1800007</v>
+      </c>
+      <c r="C1790" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D1790" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1791" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1791" s="2">
+        <v>1800008</v>
+      </c>
+      <c r="C1791" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1791" s="3">
+        <v>10230</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1792" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1792" s="2">
+        <v>1800009</v>
+      </c>
+      <c r="C1792" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D1792" s="3">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1793" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1793" s="2">
+        <v>1800010</v>
+      </c>
+      <c r="C1793" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D1793" s="3">
+        <v>6863</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1794" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1794" s="2">
+        <v>1800011</v>
+      </c>
+      <c r="C1794" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1794" s="3">
+        <v>13235</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1795" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1795" s="2">
+        <v>1800012</v>
+      </c>
+      <c r="C1795" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D1795" s="3">
+        <v>8235</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1796" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1796" s="2">
+        <v>1800013</v>
+      </c>
+      <c r="C1796" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1796" s="3">
+        <v>49100</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1797" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1797" s="2">
+        <v>1800014</v>
+      </c>
+      <c r="C1797" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D1797" s="3">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1798" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1798" s="2">
+        <v>1800015</v>
+      </c>
+      <c r="C1798" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1798" s="3">
+        <v>66700</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1799" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1799" s="2">
+        <v>1900013</v>
+      </c>
+      <c r="C1799" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D1799" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1800" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1800" s="2">
+        <v>1900018</v>
+      </c>
+      <c r="C1800" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D1800" s="3">
         <v>0</v>
       </c>
     </row>

--- a/data/업로드양식_원료단가사용.xlsx
+++ b/data/업로드양식_원료단가사용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\업무\36. 개발노트\원료비원인분석\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17BB63F-30E4-4B55-99E0-AB98C52D1CFE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F87BB18-6298-43A5-9C7E-E0ED70AD773C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34014,7 +34014,7 @@
         <v>0</v>
       </c>
       <c r="F1543" s="3">
-        <f t="shared" ref="F1543" si="24">E1543*D1543</f>
+        <f t="shared" ref="F1543:F1606" si="24">E1543*D1543</f>
         <v>0</v>
       </c>
     </row>
@@ -34031,6 +34031,13 @@
       <c r="D1544" s="3">
         <v>701</v>
       </c>
+      <c r="E1544" s="3">
+        <v>128470</v>
+      </c>
+      <c r="F1544" s="3">
+        <f t="shared" si="24"/>
+        <v>90057470</v>
+      </c>
     </row>
     <row r="1545" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1545" s="4" t="s">
@@ -34045,6 +34052,13 @@
       <c r="D1545" s="3">
         <v>19100</v>
       </c>
+      <c r="E1545" s="3">
+        <v>952.78</v>
+      </c>
+      <c r="F1545" s="3">
+        <f t="shared" si="24"/>
+        <v>18198098</v>
+      </c>
     </row>
     <row r="1546" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1546" s="4" t="s">
@@ -34059,6 +34073,13 @@
       <c r="D1546" s="3">
         <v>1373</v>
       </c>
+      <c r="E1546" s="3">
+        <v>1480</v>
+      </c>
+      <c r="F1546" s="3">
+        <f t="shared" si="24"/>
+        <v>2032040</v>
+      </c>
     </row>
     <row r="1547" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1547" s="4" t="s">
@@ -34073,6 +34094,13 @@
       <c r="D1547" s="3">
         <v>9608</v>
       </c>
+      <c r="E1547" s="3">
+        <v>272</v>
+      </c>
+      <c r="F1547" s="3">
+        <f t="shared" si="24"/>
+        <v>2613376</v>
+      </c>
     </row>
     <row r="1548" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1548" s="4" t="s">
@@ -34087,6 +34115,13 @@
       <c r="D1548" s="3">
         <v>6373</v>
       </c>
+      <c r="E1548" s="3">
+        <v>5956.8</v>
+      </c>
+      <c r="F1548" s="3">
+        <f t="shared" si="24"/>
+        <v>37962686.399999999</v>
+      </c>
     </row>
     <row r="1549" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1549" s="4" t="s">
@@ -34101,6 +34136,13 @@
       <c r="D1549" s="3">
         <v>4314</v>
       </c>
+      <c r="E1549" s="3">
+        <v>1072</v>
+      </c>
+      <c r="F1549" s="3">
+        <f t="shared" si="24"/>
+        <v>4624608</v>
+      </c>
     </row>
     <row r="1550" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1550" s="4" t="s">
@@ -34115,6 +34157,13 @@
       <c r="D1550" s="3">
         <v>882</v>
       </c>
+      <c r="E1550" s="3">
+        <v>370</v>
+      </c>
+      <c r="F1550" s="3">
+        <f t="shared" si="24"/>
+        <v>326340</v>
+      </c>
     </row>
     <row r="1551" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1551" s="4" t="s">
@@ -34129,6 +34178,13 @@
       <c r="D1551" s="3">
         <v>1422</v>
       </c>
+      <c r="E1551" s="3">
+        <v>430</v>
+      </c>
+      <c r="F1551" s="3">
+        <f t="shared" si="24"/>
+        <v>611460</v>
+      </c>
     </row>
     <row r="1552" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1552" s="4" t="s">
@@ -34143,8 +34199,15 @@
       <c r="D1552" s="3">
         <v>3627</v>
       </c>
-    </row>
-    <row r="1553" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1552" s="3">
+        <v>10662.5</v>
+      </c>
+      <c r="F1552" s="3">
+        <f t="shared" si="24"/>
+        <v>38672887.5</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1553" s="4" t="s">
         <v>390</v>
       </c>
@@ -34157,8 +34220,15 @@
       <c r="D1553" s="3">
         <v>9975</v>
       </c>
-    </row>
-    <row r="1554" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1553" s="3">
+        <v>232.5</v>
+      </c>
+      <c r="F1553" s="3">
+        <f t="shared" si="24"/>
+        <v>2319187.5</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1554" s="4" t="s">
         <v>390</v>
       </c>
@@ -34171,8 +34241,15 @@
       <c r="D1554" s="3">
         <v>980</v>
       </c>
-    </row>
-    <row r="1555" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1554" s="3">
+        <v>25092.01</v>
+      </c>
+      <c r="F1554" s="3">
+        <f t="shared" si="24"/>
+        <v>24590169.799999997</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1555" s="4" t="s">
         <v>390</v>
       </c>
@@ -34185,8 +34262,15 @@
       <c r="D1555" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1556" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1555" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1555" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1556" s="4" t="s">
         <v>390</v>
       </c>
@@ -34199,8 +34283,15 @@
       <c r="D1556" s="3">
         <v>4902</v>
       </c>
-    </row>
-    <row r="1557" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1556" s="3">
+        <v>830</v>
+      </c>
+      <c r="F1556" s="3">
+        <f t="shared" si="24"/>
+        <v>4068660</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1557" s="4" t="s">
         <v>390</v>
       </c>
@@ -34213,8 +34304,15 @@
       <c r="D1557" s="3">
         <v>686</v>
       </c>
-    </row>
-    <row r="1558" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1557" s="3">
+        <v>840</v>
+      </c>
+      <c r="F1557" s="3">
+        <f t="shared" si="24"/>
+        <v>576240</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1558" s="4" t="s">
         <v>390</v>
       </c>
@@ -34227,8 +34325,15 @@
       <c r="D1558" s="3">
         <v>9449</v>
       </c>
-    </row>
-    <row r="1559" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1558" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1558" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1559" s="4" t="s">
         <v>390</v>
       </c>
@@ -34241,8 +34346,15 @@
       <c r="D1559" s="3">
         <v>4804</v>
       </c>
-    </row>
-    <row r="1560" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1559" s="3">
+        <v>1660</v>
+      </c>
+      <c r="F1559" s="3">
+        <f t="shared" si="24"/>
+        <v>7974640</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1560" s="4" t="s">
         <v>390</v>
       </c>
@@ -34255,8 +34367,15 @@
       <c r="D1560" s="3">
         <v>11667</v>
       </c>
-    </row>
-    <row r="1561" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1560" s="3">
+        <v>3435.6</v>
+      </c>
+      <c r="F1560" s="3">
+        <f t="shared" si="24"/>
+        <v>40083145.199999996</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1561" s="4" t="s">
         <v>390</v>
       </c>
@@ -34269,8 +34388,15 @@
       <c r="D1561" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="1562" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1561" s="3">
+        <v>5837.15</v>
+      </c>
+      <c r="F1561" s="3">
+        <f t="shared" si="24"/>
+        <v>32688039.999999996</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1562" s="4" t="s">
         <v>390</v>
       </c>
@@ -34283,8 +34409,15 @@
       <c r="D1562" s="3">
         <v>2575</v>
       </c>
-    </row>
-    <row r="1563" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1562" s="3">
+        <v>11245.483</v>
+      </c>
+      <c r="F1562" s="3">
+        <f t="shared" si="24"/>
+        <v>28957118.725000001</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1563" s="4" t="s">
         <v>390</v>
       </c>
@@ -34297,8 +34430,15 @@
       <c r="D1563" s="3">
         <v>3400</v>
       </c>
-    </row>
-    <row r="1564" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1563" s="3">
+        <v>4265.49</v>
+      </c>
+      <c r="F1563" s="3">
+        <f t="shared" si="24"/>
+        <v>14502666</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1564" s="4" t="s">
         <v>390</v>
       </c>
@@ -34311,8 +34451,15 @@
       <c r="D1564" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1565" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1564" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1564" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1565" s="4" t="s">
         <v>390</v>
       </c>
@@ -34325,8 +34472,15 @@
       <c r="D1565" s="3">
         <v>2843</v>
       </c>
-    </row>
-    <row r="1566" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1565" s="3">
+        <v>2593.7600000000002</v>
+      </c>
+      <c r="F1565" s="3">
+        <f t="shared" si="24"/>
+        <v>7374059.6800000006</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1566" s="4" t="s">
         <v>390</v>
       </c>
@@ -34339,8 +34493,15 @@
       <c r="D1566" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1567" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1566" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1566" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1567" s="4" t="s">
         <v>390</v>
       </c>
@@ -34353,8 +34514,15 @@
       <c r="D1567" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1568" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1567" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1567" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1568" s="4" t="s">
         <v>390</v>
       </c>
@@ -34367,8 +34535,15 @@
       <c r="D1568" s="3">
         <v>5000</v>
       </c>
-    </row>
-    <row r="1569" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1568" s="3">
+        <v>53.87</v>
+      </c>
+      <c r="F1568" s="3">
+        <f t="shared" si="24"/>
+        <v>269350</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1569" s="4" t="s">
         <v>390</v>
       </c>
@@ -34381,8 +34556,15 @@
       <c r="D1569" s="3">
         <v>6200</v>
       </c>
-    </row>
-    <row r="1570" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1569" s="3">
+        <v>60.24</v>
+      </c>
+      <c r="F1569" s="3">
+        <f t="shared" si="24"/>
+        <v>373488</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1570" s="4" t="s">
         <v>390</v>
       </c>
@@ -34395,8 +34577,15 @@
       <c r="D1570" s="3">
         <v>4600</v>
       </c>
-    </row>
-    <row r="1571" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1570" s="3">
+        <v>398.40800000000002</v>
+      </c>
+      <c r="F1570" s="3">
+        <f t="shared" si="24"/>
+        <v>1832676.8</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1571" s="4" t="s">
         <v>390</v>
       </c>
@@ -34409,8 +34598,15 @@
       <c r="D1571" s="3">
         <v>1127</v>
       </c>
-    </row>
-    <row r="1572" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1571" s="3">
+        <v>79430</v>
+      </c>
+      <c r="F1571" s="3">
+        <f t="shared" si="24"/>
+        <v>89517610</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1572" s="4" t="s">
         <v>390</v>
       </c>
@@ -34423,8 +34619,15 @@
       <c r="D1572" s="3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="1573" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1572" s="3">
+        <v>38401</v>
+      </c>
+      <c r="F1572" s="3">
+        <f t="shared" si="24"/>
+        <v>115203000</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1573" s="4" t="s">
         <v>390</v>
       </c>
@@ -34437,8 +34640,15 @@
       <c r="D1573" s="3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="1574" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1573" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1573" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1574" s="4" t="s">
         <v>390</v>
       </c>
@@ -34451,8 +34661,15 @@
       <c r="D1574" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1575" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1574" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1574" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1575" s="4" t="s">
         <v>390</v>
       </c>
@@ -34465,8 +34682,15 @@
       <c r="D1575" s="3">
         <v>1176</v>
       </c>
-    </row>
-    <row r="1576" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1575" s="3">
+        <v>13430</v>
+      </c>
+      <c r="F1575" s="3">
+        <f t="shared" si="24"/>
+        <v>15793680</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1576" s="4" t="s">
         <v>390</v>
       </c>
@@ -34479,8 +34703,15 @@
       <c r="D1576" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1577" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1576" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1576" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1577" s="4" t="s">
         <v>390</v>
       </c>
@@ -34493,8 +34724,15 @@
       <c r="D1577" s="3">
         <v>1450</v>
       </c>
-    </row>
-    <row r="1578" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1577" s="3">
+        <v>18460.54</v>
+      </c>
+      <c r="F1577" s="3">
+        <f t="shared" si="24"/>
+        <v>26767783</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1578" s="4" t="s">
         <v>390</v>
       </c>
@@ -34507,8 +34745,15 @@
       <c r="D1578" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1579" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1578" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1578" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1579" s="4" t="s">
         <v>390</v>
       </c>
@@ -34521,8 +34766,15 @@
       <c r="D1579" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1580" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1579" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1579" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1580" s="4" t="s">
         <v>390</v>
       </c>
@@ -34535,8 +34787,15 @@
       <c r="D1580" s="3">
         <v>8583</v>
       </c>
-    </row>
-    <row r="1581" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1580" s="3">
+        <v>120</v>
+      </c>
+      <c r="F1580" s="3">
+        <f t="shared" si="24"/>
+        <v>1029960</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1581" s="4" t="s">
         <v>390</v>
       </c>
@@ -34549,8 +34808,15 @@
       <c r="D1581" s="3">
         <v>1617</v>
       </c>
-    </row>
-    <row r="1582" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1581" s="3">
+        <v>16145</v>
+      </c>
+      <c r="F1581" s="3">
+        <f t="shared" si="24"/>
+        <v>26106465</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1582" s="4" t="s">
         <v>390</v>
       </c>
@@ -34563,8 +34829,15 @@
       <c r="D1582" s="3">
         <v>3350</v>
       </c>
-    </row>
-    <row r="1583" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1582" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1582" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1583" s="4" t="s">
         <v>390</v>
       </c>
@@ -34577,8 +34850,15 @@
       <c r="D1583" s="3">
         <v>31000</v>
       </c>
-    </row>
-    <row r="1584" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1583" s="3">
+        <v>580.69000000000005</v>
+      </c>
+      <c r="F1583" s="3">
+        <f t="shared" si="24"/>
+        <v>18001390</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1584" s="4" t="s">
         <v>390</v>
       </c>
@@ -34591,8 +34871,15 @@
       <c r="D1584" s="3">
         <v>11275</v>
       </c>
-    </row>
-    <row r="1585" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1584" s="3">
+        <v>1</v>
+      </c>
+      <c r="F1584" s="3">
+        <f t="shared" si="24"/>
+        <v>11275</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1585" s="4" t="s">
         <v>390</v>
       </c>
@@ -34605,8 +34892,15 @@
       <c r="D1585" s="3">
         <v>9804</v>
       </c>
-    </row>
-    <row r="1586" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1585" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1585" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1586" s="4" t="s">
         <v>390</v>
       </c>
@@ -34619,8 +34913,15 @@
       <c r="D1586" s="3">
         <v>8824</v>
       </c>
-    </row>
-    <row r="1587" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1586" s="3">
+        <v>176.29</v>
+      </c>
+      <c r="F1586" s="3">
+        <f t="shared" si="24"/>
+        <v>1555582.96</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1587" s="4" t="s">
         <v>390</v>
       </c>
@@ -34633,8 +34934,15 @@
       <c r="D1587" s="3">
         <v>10784</v>
       </c>
-    </row>
-    <row r="1588" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1587" s="3">
+        <v>5.49</v>
+      </c>
+      <c r="F1587" s="3">
+        <f t="shared" si="24"/>
+        <v>59204.160000000003</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1588" s="4" t="s">
         <v>390</v>
       </c>
@@ -34647,8 +34955,15 @@
       <c r="D1588" s="3">
         <v>17647</v>
       </c>
-    </row>
-    <row r="1589" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1588" s="3">
+        <v>1.91</v>
+      </c>
+      <c r="F1588" s="3">
+        <f t="shared" si="24"/>
+        <v>33705.769999999997</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1589" s="4" t="s">
         <v>390</v>
       </c>
@@ -34661,8 +34976,15 @@
       <c r="D1589" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1590" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1589" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1589" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1590" s="4" t="s">
         <v>390</v>
       </c>
@@ -34675,8 +34997,15 @@
       <c r="D1590" s="3">
         <v>14706</v>
       </c>
-    </row>
-    <row r="1591" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1590" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1590" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1591" s="4" t="s">
         <v>390</v>
       </c>
@@ -34689,8 +35018,15 @@
       <c r="D1591" s="3">
         <v>21000</v>
       </c>
-    </row>
-    <row r="1592" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1591" s="3">
+        <v>35.85</v>
+      </c>
+      <c r="F1591" s="3">
+        <f t="shared" si="24"/>
+        <v>752850</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1592" s="4" t="s">
         <v>390</v>
       </c>
@@ -34703,8 +35039,15 @@
       <c r="D1592" s="3">
         <v>11000</v>
       </c>
-    </row>
-    <row r="1593" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1592" s="3">
+        <v>834.15</v>
+      </c>
+      <c r="F1592" s="3">
+        <f t="shared" si="24"/>
+        <v>9175650</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1593" s="4" t="s">
         <v>390</v>
       </c>
@@ -34717,8 +35060,15 @@
       <c r="D1593" s="3">
         <v>54000</v>
       </c>
-    </row>
-    <row r="1594" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1593" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="F1593" s="3">
+        <f t="shared" si="24"/>
+        <v>361800</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1594" s="4" t="s">
         <v>390</v>
       </c>
@@ -34731,8 +35081,15 @@
       <c r="D1594" s="3">
         <v>77321</v>
       </c>
-    </row>
-    <row r="1595" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1594" s="3">
+        <v>7.13</v>
+      </c>
+      <c r="F1594" s="3">
+        <f t="shared" si="24"/>
+        <v>551298.73</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1595" s="4" t="s">
         <v>390</v>
       </c>
@@ -34745,8 +35102,15 @@
       <c r="D1595" s="3">
         <v>58000</v>
       </c>
-    </row>
-    <row r="1596" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1595" s="3">
+        <v>68</v>
+      </c>
+      <c r="F1595" s="3">
+        <f t="shared" si="24"/>
+        <v>3944000</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1596" s="4" t="s">
         <v>390</v>
       </c>
@@ -34759,8 +35123,15 @@
       <c r="D1596" s="3">
         <v>60760</v>
       </c>
-    </row>
-    <row r="1597" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1596" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1596" s="3">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1597" s="4" t="s">
         <v>390</v>
       </c>
@@ -34773,8 +35144,15 @@
       <c r="D1597" s="3">
         <v>97750</v>
       </c>
-    </row>
-    <row r="1598" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1597" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="F1597" s="3">
+        <f t="shared" si="24"/>
+        <v>733125</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1598" s="4" t="s">
         <v>390</v>
       </c>
@@ -34787,8 +35165,15 @@
       <c r="D1598" s="3">
         <v>6400</v>
       </c>
-    </row>
-    <row r="1599" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1598" s="3">
+        <v>359.42</v>
+      </c>
+      <c r="F1598" s="3">
+        <f t="shared" si="24"/>
+        <v>2300288</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1599" s="4" t="s">
         <v>390</v>
       </c>
@@ -34801,8 +35186,15 @@
       <c r="D1599" s="3">
         <v>6300</v>
       </c>
-    </row>
-    <row r="1600" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1599" s="3">
+        <v>9956</v>
+      </c>
+      <c r="F1599" s="3">
+        <f t="shared" si="24"/>
+        <v>62722800</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1600" s="4" t="s">
         <v>390</v>
       </c>
@@ -34815,8 +35207,15 @@
       <c r="D1600" s="3">
         <v>6000</v>
       </c>
-    </row>
-    <row r="1601" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1600" s="3">
+        <v>15493</v>
+      </c>
+      <c r="F1600" s="3">
+        <f t="shared" si="24"/>
+        <v>92958000</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1601" s="4" t="s">
         <v>390</v>
       </c>
@@ -34829,8 +35228,15 @@
       <c r="D1601" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="1602" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1601" s="3">
+        <v>15156</v>
+      </c>
+      <c r="F1601" s="3">
+        <f t="shared" si="24"/>
+        <v>39405600</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1602" s="4" t="s">
         <v>390</v>
       </c>
@@ -34843,8 +35249,15 @@
       <c r="D1602" s="3">
         <v>14510</v>
       </c>
-    </row>
-    <row r="1603" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1602" s="3">
+        <v>5649.51</v>
+      </c>
+      <c r="F1602" s="3">
+        <f t="shared" si="24"/>
+        <v>81974390.100000009</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1603" s="4" t="s">
         <v>390</v>
       </c>
@@ -34857,8 +35270,15 @@
       <c r="D1603" s="3">
         <v>885</v>
       </c>
-    </row>
-    <row r="1604" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1603" s="3">
+        <v>105214</v>
+      </c>
+      <c r="F1603" s="3">
+        <f t="shared" si="24"/>
+        <v>93114390</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1604" s="4" t="s">
         <v>390</v>
       </c>
@@ -34871,8 +35291,15 @@
       <c r="D1604" s="3">
         <v>1216</v>
       </c>
-    </row>
-    <row r="1605" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1604" s="3">
+        <v>30289</v>
+      </c>
+      <c r="F1604" s="3">
+        <f t="shared" si="24"/>
+        <v>36831424</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1605" s="4" t="s">
         <v>390</v>
       </c>
@@ -34885,8 +35312,15 @@
       <c r="D1605" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="1606" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1605" s="3">
+        <v>23373.11</v>
+      </c>
+      <c r="F1605" s="3">
+        <f t="shared" si="24"/>
+        <v>51420842</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1606" s="4" t="s">
         <v>390</v>
       </c>
@@ -34899,8 +35333,15 @@
       <c r="D1606" s="3">
         <v>75000</v>
       </c>
-    </row>
-    <row r="1607" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1606" s="3">
+        <v>20.654</v>
+      </c>
+      <c r="F1606" s="3">
+        <f t="shared" si="24"/>
+        <v>1549050</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1607" s="4" t="s">
         <v>390</v>
       </c>
@@ -34913,8 +35354,15 @@
       <c r="D1607" s="3">
         <v>33000</v>
       </c>
-    </row>
-    <row r="1608" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1607" s="3">
+        <v>99.95</v>
+      </c>
+      <c r="F1607" s="3">
+        <f t="shared" ref="F1607:F1670" si="25">E1607*D1607</f>
+        <v>3298350</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1608" s="4" t="s">
         <v>390</v>
       </c>
@@ -34927,8 +35375,15 @@
       <c r="D1608" s="3">
         <v>118000</v>
       </c>
-    </row>
-    <row r="1609" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1608" s="3">
+        <v>18.989999999999998</v>
+      </c>
+      <c r="F1608" s="3">
+        <f t="shared" si="25"/>
+        <v>2240820</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1609" s="4" t="s">
         <v>390</v>
       </c>
@@ -34941,8 +35396,15 @@
       <c r="D1609" s="3">
         <v>6471</v>
       </c>
-    </row>
-    <row r="1610" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1609" s="3">
+        <v>692.52</v>
+      </c>
+      <c r="F1609" s="3">
+        <f t="shared" si="25"/>
+        <v>4481296.92</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1610" s="4" t="s">
         <v>390</v>
       </c>
@@ -34955,8 +35417,15 @@
       <c r="D1610" s="3">
         <v>38235</v>
       </c>
-    </row>
-    <row r="1611" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1610" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1610" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1611" s="4" t="s">
         <v>390</v>
       </c>
@@ -34969,8 +35438,15 @@
       <c r="D1611" s="3">
         <v>4000</v>
       </c>
-    </row>
-    <row r="1612" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1611" s="3">
+        <v>564.56700000000001</v>
+      </c>
+      <c r="F1611" s="3">
+        <f t="shared" si="25"/>
+        <v>2258268</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1612" s="4" t="s">
         <v>390</v>
       </c>
@@ -34983,8 +35459,15 @@
       <c r="D1612" s="3">
         <v>43000</v>
       </c>
-    </row>
-    <row r="1613" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1612" s="3">
+        <v>172.63200000000001</v>
+      </c>
+      <c r="F1612" s="3">
+        <f t="shared" si="25"/>
+        <v>7423176</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1613" s="4" t="s">
         <v>390</v>
       </c>
@@ -34997,8 +35480,15 @@
       <c r="D1613" s="3">
         <v>15478</v>
       </c>
-    </row>
-    <row r="1614" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1613" s="3">
+        <v>1029.366</v>
+      </c>
+      <c r="F1613" s="3">
+        <f t="shared" si="25"/>
+        <v>15932526.947999999</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1614" s="4" t="s">
         <v>390</v>
       </c>
@@ -35011,8 +35501,15 @@
       <c r="D1614" s="3">
         <v>5500</v>
       </c>
-    </row>
-    <row r="1615" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1614" s="3">
+        <v>910.08</v>
+      </c>
+      <c r="F1614" s="3">
+        <f t="shared" si="25"/>
+        <v>5005440</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1615" s="4" t="s">
         <v>390</v>
       </c>
@@ -35025,8 +35522,15 @@
       <c r="D1615" s="3">
         <v>36000</v>
       </c>
-    </row>
-    <row r="1616" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1615" s="3">
+        <v>78.67</v>
+      </c>
+      <c r="F1615" s="3">
+        <f t="shared" si="25"/>
+        <v>2832120</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1616" s="4" t="s">
         <v>390</v>
       </c>
@@ -35039,8 +35543,15 @@
       <c r="D1616" s="3">
         <v>35000</v>
       </c>
-    </row>
-    <row r="1617" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1616" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1616" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1617" s="4" t="s">
         <v>390</v>
       </c>
@@ -35053,8 +35564,15 @@
       <c r="D1617" s="3">
         <v>12000</v>
       </c>
-    </row>
-    <row r="1618" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1617" s="3">
+        <v>1117.5899999999999</v>
+      </c>
+      <c r="F1617" s="3">
+        <f t="shared" si="25"/>
+        <v>13411079.999999998</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1618" s="4" t="s">
         <v>390</v>
       </c>
@@ -35067,8 +35585,15 @@
       <c r="D1618" s="3">
         <v>540</v>
       </c>
-    </row>
-    <row r="1619" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1618" s="3">
+        <v>2673.77</v>
+      </c>
+      <c r="F1618" s="3">
+        <f t="shared" si="25"/>
+        <v>1443835.8</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1619" s="4" t="s">
         <v>390</v>
       </c>
@@ -35081,8 +35606,15 @@
       <c r="D1619" s="3">
         <v>1550</v>
       </c>
-    </row>
-    <row r="1620" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1619" s="3">
+        <v>4023.76</v>
+      </c>
+      <c r="F1619" s="3">
+        <f t="shared" si="25"/>
+        <v>6236828</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1620" s="4" t="s">
         <v>390</v>
       </c>
@@ -35095,8 +35627,15 @@
       <c r="D1620" s="3">
         <v>3150</v>
       </c>
-    </row>
-    <row r="1621" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1620" s="3">
+        <v>6959</v>
+      </c>
+      <c r="F1620" s="3">
+        <f t="shared" si="25"/>
+        <v>21920850</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1621" s="4" t="s">
         <v>390</v>
       </c>
@@ -35109,8 +35648,15 @@
       <c r="D1621" s="3">
         <v>3150</v>
       </c>
-    </row>
-    <row r="1622" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1621" s="3">
+        <v>4939.1000000000004</v>
+      </c>
+      <c r="F1621" s="3">
+        <f t="shared" si="25"/>
+        <v>15558165.000000002</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1622" s="4" t="s">
         <v>390</v>
       </c>
@@ -35123,8 +35669,15 @@
       <c r="D1622" s="3">
         <v>4200</v>
       </c>
-    </row>
-    <row r="1623" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1622" s="3">
+        <v>2855.23</v>
+      </c>
+      <c r="F1622" s="3">
+        <f t="shared" si="25"/>
+        <v>11991966</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1623" s="4" t="s">
         <v>390</v>
       </c>
@@ -35137,8 +35690,15 @@
       <c r="D1623" s="3">
         <v>38600</v>
       </c>
-    </row>
-    <row r="1624" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1623" s="3">
+        <v>519.74800000000005</v>
+      </c>
+      <c r="F1623" s="3">
+        <f t="shared" si="25"/>
+        <v>20062272.800000001</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1624" s="4" t="s">
         <v>390</v>
       </c>
@@ -35151,8 +35711,15 @@
       <c r="D1624" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1625" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1624" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1624" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1625" s="4" t="s">
         <v>390</v>
       </c>
@@ -35165,8 +35732,15 @@
       <c r="D1625" s="3">
         <v>43500</v>
       </c>
-    </row>
-    <row r="1626" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1625" s="3">
+        <v>520.29499999999996</v>
+      </c>
+      <c r="F1625" s="3">
+        <f t="shared" si="25"/>
+        <v>22632832.5</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1626" s="4" t="s">
         <v>390</v>
       </c>
@@ -35179,8 +35753,15 @@
       <c r="D1626" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1627" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1626" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1626" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1627" s="4" t="s">
         <v>390</v>
       </c>
@@ -35193,8 +35774,15 @@
       <c r="D1627" s="3">
         <v>40000</v>
       </c>
-    </row>
-    <row r="1628" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1627" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1627" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1628" s="4" t="s">
         <v>390</v>
       </c>
@@ -35207,8 +35795,15 @@
       <c r="D1628" s="3">
         <v>35000</v>
       </c>
-    </row>
-    <row r="1629" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1628" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1628" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1629" s="4" t="s">
         <v>390</v>
       </c>
@@ -35221,8 +35816,15 @@
       <c r="D1629" s="3">
         <v>15800</v>
       </c>
-    </row>
-    <row r="1630" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1629" s="3">
+        <v>30.32</v>
+      </c>
+      <c r="F1629" s="3">
+        <f t="shared" si="25"/>
+        <v>479056</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1630" s="4" t="s">
         <v>390</v>
       </c>
@@ -35235,8 +35837,15 @@
       <c r="D1630" s="3">
         <v>98000</v>
       </c>
-    </row>
-    <row r="1631" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1630" s="3">
+        <v>2.91</v>
+      </c>
+      <c r="F1630" s="3">
+        <f t="shared" si="25"/>
+        <v>285180</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1631" s="4" t="s">
         <v>390</v>
       </c>
@@ -35249,8 +35858,15 @@
       <c r="D1631" s="3">
         <v>23000</v>
       </c>
-    </row>
-    <row r="1632" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1631" s="3">
+        <v>5.85</v>
+      </c>
+      <c r="F1631" s="3">
+        <f t="shared" si="25"/>
+        <v>134550</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1632" s="4" t="s">
         <v>390</v>
       </c>
@@ -35263,8 +35879,15 @@
       <c r="D1632" s="3">
         <v>64706</v>
       </c>
-    </row>
-    <row r="1633" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1632" s="3">
+        <v>23.45</v>
+      </c>
+      <c r="F1632" s="3">
+        <f t="shared" si="25"/>
+        <v>1517355.7</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1633" s="4" t="s">
         <v>390</v>
       </c>
@@ -35277,8 +35900,15 @@
       <c r="D1633" s="3">
         <v>32000</v>
       </c>
-    </row>
-    <row r="1634" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1633" s="3">
+        <v>227.07</v>
+      </c>
+      <c r="F1633" s="3">
+        <f t="shared" si="25"/>
+        <v>7266240</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1634" s="4" t="s">
         <v>390</v>
       </c>
@@ -35291,8 +35921,15 @@
       <c r="D1634" s="3">
         <v>37000</v>
       </c>
-    </row>
-    <row r="1635" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1634" s="3">
+        <v>219.72</v>
+      </c>
+      <c r="F1634" s="3">
+        <f t="shared" si="25"/>
+        <v>8129640</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1635" s="4" t="s">
         <v>390</v>
       </c>
@@ -35305,8 +35942,15 @@
       <c r="D1635" s="3">
         <v>66000</v>
       </c>
-    </row>
-    <row r="1636" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1635" s="3">
+        <v>397.09</v>
+      </c>
+      <c r="F1635" s="3">
+        <f t="shared" si="25"/>
+        <v>26207940</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1636" s="4" t="s">
         <v>390</v>
       </c>
@@ -35319,8 +35963,15 @@
       <c r="D1636" s="3">
         <v>9300</v>
       </c>
-    </row>
-    <row r="1637" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1636" s="3">
+        <v>4634.09</v>
+      </c>
+      <c r="F1636" s="3">
+        <f t="shared" si="25"/>
+        <v>43097037</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1637" s="4" t="s">
         <v>390</v>
       </c>
@@ -35333,8 +35984,15 @@
       <c r="D1637" s="3">
         <v>45000</v>
       </c>
-    </row>
-    <row r="1638" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1637" s="3">
+        <v>142.72999999999999</v>
+      </c>
+      <c r="F1637" s="3">
+        <f t="shared" si="25"/>
+        <v>6422850</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1638" s="4" t="s">
         <v>390</v>
       </c>
@@ -35347,8 +36005,15 @@
       <c r="D1638" s="3">
         <v>36000</v>
       </c>
-    </row>
-    <row r="1639" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1638" s="3">
+        <v>25.89</v>
+      </c>
+      <c r="F1638" s="3">
+        <f t="shared" si="25"/>
+        <v>932040</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1639" s="4" t="s">
         <v>390</v>
       </c>
@@ -35361,8 +36026,15 @@
       <c r="D1639" s="3">
         <v>5400</v>
       </c>
-    </row>
-    <row r="1640" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1639" s="3">
+        <v>698.76</v>
+      </c>
+      <c r="F1639" s="3">
+        <f t="shared" si="25"/>
+        <v>3773304</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1640" s="4" t="s">
         <v>390</v>
       </c>
@@ -35375,8 +36047,15 @@
       <c r="D1640" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="1641" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1640" s="3">
+        <v>19651.38</v>
+      </c>
+      <c r="F1640" s="3">
+        <f t="shared" si="25"/>
+        <v>110047728</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1641" s="4" t="s">
         <v>390</v>
       </c>
@@ -35389,8 +36068,15 @@
       <c r="D1641" s="3">
         <v>4800</v>
       </c>
-    </row>
-    <row r="1642" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1641" s="3">
+        <v>4283.62</v>
+      </c>
+      <c r="F1641" s="3">
+        <f t="shared" si="25"/>
+        <v>20561376</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1642" s="4" t="s">
         <v>390</v>
       </c>
@@ -35403,8 +36089,15 @@
       <c r="D1642" s="3">
         <v>21000</v>
       </c>
-    </row>
-    <row r="1643" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1642" s="3">
+        <v>123.81</v>
+      </c>
+      <c r="F1642" s="3">
+        <f t="shared" si="25"/>
+        <v>2600010</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1643" s="4" t="s">
         <v>390</v>
       </c>
@@ -35417,8 +36110,15 @@
       <c r="D1643" s="3">
         <v>4300</v>
       </c>
-    </row>
-    <row r="1644" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1643" s="3">
+        <v>589.79</v>
+      </c>
+      <c r="F1643" s="3">
+        <f t="shared" si="25"/>
+        <v>2536097</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1644" s="4" t="s">
         <v>390</v>
       </c>
@@ -35431,8 +36131,15 @@
       <c r="D1644" s="3">
         <v>7000</v>
       </c>
-    </row>
-    <row r="1645" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1644" s="3">
+        <v>313.37</v>
+      </c>
+      <c r="F1644" s="3">
+        <f t="shared" si="25"/>
+        <v>2193590</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1645" s="4" t="s">
         <v>390</v>
       </c>
@@ -35445,8 +36152,15 @@
       <c r="D1645" s="3">
         <v>4402</v>
       </c>
-    </row>
-    <row r="1646" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1645" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1645" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1646" s="4" t="s">
         <v>390</v>
       </c>
@@ -35459,8 +36173,15 @@
       <c r="D1646" s="3">
         <v>14014</v>
       </c>
-    </row>
-    <row r="1647" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1646" s="3">
+        <v>27.49</v>
+      </c>
+      <c r="F1646" s="3">
+        <f t="shared" si="25"/>
+        <v>385244.86</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1647" s="4" t="s">
         <v>390</v>
       </c>
@@ -35473,8 +36194,15 @@
       <c r="D1647" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1648" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1647" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1647" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1648" s="4" t="s">
         <v>390</v>
       </c>
@@ -35487,8 +36215,15 @@
       <c r="D1648" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1649" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1648" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1648" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1649" s="4" t="s">
         <v>390</v>
       </c>
@@ -35501,8 +36236,15 @@
       <c r="D1649" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1650" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1649" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1649" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1650" s="4" t="s">
         <v>390</v>
       </c>
@@ -35515,8 +36257,15 @@
       <c r="D1650" s="3">
         <v>2470</v>
       </c>
-    </row>
-    <row r="1651" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1650" s="3">
+        <v>1.3979999999999999</v>
+      </c>
+      <c r="F1650" s="3">
+        <f t="shared" si="25"/>
+        <v>3453.06</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1651" s="4" t="s">
         <v>390</v>
       </c>
@@ -35529,8 +36278,15 @@
       <c r="D1651" s="3">
         <v>450000</v>
       </c>
-    </row>
-    <row r="1652" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1651" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1651" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1652" s="4" t="s">
         <v>390</v>
       </c>
@@ -35543,8 +36299,15 @@
       <c r="D1652" s="3">
         <v>190000</v>
       </c>
-    </row>
-    <row r="1653" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1652" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1652" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1653" s="4" t="s">
         <v>390</v>
       </c>
@@ -35557,8 +36320,15 @@
       <c r="D1653" s="3">
         <v>27000</v>
       </c>
-    </row>
-    <row r="1654" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1653" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1653" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1654" s="4" t="s">
         <v>390</v>
       </c>
@@ -35571,8 +36341,15 @@
       <c r="D1654" s="3">
         <v>33000</v>
       </c>
-    </row>
-    <row r="1655" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1654" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1654" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1655" s="4" t="s">
         <v>390</v>
       </c>
@@ -35585,8 +36362,15 @@
       <c r="D1655" s="3">
         <v>47000</v>
       </c>
-    </row>
-    <row r="1656" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1655" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1655" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1656" s="4" t="s">
         <v>390</v>
       </c>
@@ -35599,8 +36383,15 @@
       <c r="D1656" s="3">
         <v>33000</v>
       </c>
-    </row>
-    <row r="1657" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1656" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1656" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1657" s="4" t="s">
         <v>390</v>
       </c>
@@ -35613,8 +36404,15 @@
       <c r="D1657" s="3">
         <v>6961</v>
       </c>
-    </row>
-    <row r="1658" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1657" s="3">
+        <v>80</v>
+      </c>
+      <c r="F1657" s="3">
+        <f t="shared" si="25"/>
+        <v>556880</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1658" s="4" t="s">
         <v>390</v>
       </c>
@@ -35627,8 +36425,15 @@
       <c r="D1658" s="3">
         <v>25490</v>
       </c>
-    </row>
-    <row r="1659" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1658" s="3">
+        <v>19.884</v>
+      </c>
+      <c r="F1658" s="3">
+        <f t="shared" si="25"/>
+        <v>506843.16000000003</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1659" s="4" t="s">
         <v>390</v>
       </c>
@@ -35641,8 +36446,15 @@
       <c r="D1659" s="3">
         <v>50187</v>
       </c>
-    </row>
-    <row r="1660" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1659" s="3">
+        <v>25</v>
+      </c>
+      <c r="F1659" s="3">
+        <f t="shared" si="25"/>
+        <v>1254675</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1660" s="4" t="s">
         <v>390</v>
       </c>
@@ -35655,8 +36467,15 @@
       <c r="D1660" s="3">
         <v>74833</v>
       </c>
-    </row>
-    <row r="1661" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1660" s="3">
+        <v>3.6070000000000002</v>
+      </c>
+      <c r="F1660" s="3">
+        <f t="shared" si="25"/>
+        <v>269922.63099999999</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1661" s="4" t="s">
         <v>390</v>
       </c>
@@ -35669,8 +36488,15 @@
       <c r="D1661" s="3">
         <v>33031</v>
       </c>
-    </row>
-    <row r="1662" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1661" s="3">
+        <v>23.291</v>
+      </c>
+      <c r="F1661" s="3">
+        <f t="shared" si="25"/>
+        <v>769325.02100000007</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1662" s="4" t="s">
         <v>390</v>
       </c>
@@ -35683,8 +36509,15 @@
       <c r="D1662" s="3">
         <v>53387</v>
       </c>
-    </row>
-    <row r="1663" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1662" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1662" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1663" s="4" t="s">
         <v>390</v>
       </c>
@@ -35697,8 +36530,15 @@
       <c r="D1663" s="3">
         <v>100500</v>
       </c>
-    </row>
-    <row r="1664" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1663" s="3">
+        <v>3.48</v>
+      </c>
+      <c r="F1663" s="3">
+        <f t="shared" si="25"/>
+        <v>349740</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1664" s="4" t="s">
         <v>390</v>
       </c>
@@ -35711,8 +36551,15 @@
       <c r="D1664" s="3">
         <v>50600</v>
       </c>
-    </row>
-    <row r="1665" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1664" s="3">
+        <v>9.7530000000000001</v>
+      </c>
+      <c r="F1664" s="3">
+        <f t="shared" si="25"/>
+        <v>493501.8</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1665" s="4" t="s">
         <v>390</v>
       </c>
@@ -35725,8 +36572,15 @@
       <c r="D1665" s="3">
         <v>3235</v>
       </c>
-    </row>
-    <row r="1666" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1665" s="3">
+        <v>178.5</v>
+      </c>
+      <c r="F1665" s="3">
+        <f t="shared" si="25"/>
+        <v>577447.5</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1666" s="4" t="s">
         <v>390</v>
       </c>
@@ -35739,8 +36593,15 @@
       <c r="D1666" s="3">
         <v>4412</v>
       </c>
-    </row>
-    <row r="1667" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1666" s="3">
+        <v>19.5</v>
+      </c>
+      <c r="F1666" s="3">
+        <f t="shared" si="25"/>
+        <v>86034</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1667" s="4" t="s">
         <v>390</v>
       </c>
@@ -35753,8 +36614,15 @@
       <c r="D1667" s="3">
         <v>3922</v>
       </c>
-    </row>
-    <row r="1668" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1667" s="3">
+        <v>295</v>
+      </c>
+      <c r="F1667" s="3">
+        <f t="shared" si="25"/>
+        <v>1156990</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1668" s="4" t="s">
         <v>390</v>
       </c>
@@ -35767,8 +36635,15 @@
       <c r="D1668" s="3">
         <v>7843</v>
       </c>
-    </row>
-    <row r="1669" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1668" s="3">
+        <v>505</v>
+      </c>
+      <c r="F1668" s="3">
+        <f t="shared" si="25"/>
+        <v>3960715</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1669" s="4" t="s">
         <v>390</v>
       </c>
@@ -35781,8 +36656,15 @@
       <c r="D1669" s="3">
         <v>30686</v>
       </c>
-    </row>
-    <row r="1670" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1669" s="3">
+        <v>3.06</v>
+      </c>
+      <c r="F1669" s="3">
+        <f t="shared" si="25"/>
+        <v>93899.16</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1670" s="4" t="s">
         <v>390</v>
       </c>
@@ -35795,8 +36677,15 @@
       <c r="D1670" s="3">
         <v>2892</v>
       </c>
-    </row>
-    <row r="1671" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1670" s="3">
+        <v>1502</v>
+      </c>
+      <c r="F1670" s="3">
+        <f t="shared" si="25"/>
+        <v>4343784</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1671" s="4" t="s">
         <v>390</v>
       </c>
@@ -35809,8 +36698,15 @@
       <c r="D1671" s="3">
         <v>26962</v>
       </c>
-    </row>
-    <row r="1672" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1671" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="F1671" s="3">
+        <f t="shared" ref="F1671:F1734" si="26">E1671*D1671</f>
+        <v>4853.16</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1672" s="4" t="s">
         <v>390</v>
       </c>
@@ -35823,8 +36719,15 @@
       <c r="D1672" s="3">
         <v>19800</v>
       </c>
-    </row>
-    <row r="1673" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1672" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1672" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1673" s="4" t="s">
         <v>390</v>
       </c>
@@ -35837,8 +36740,15 @@
       <c r="D1673" s="3">
         <v>75683</v>
       </c>
-    </row>
-    <row r="1674" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1673" s="3">
+        <v>17.809999999999999</v>
+      </c>
+      <c r="F1673" s="3">
+        <f t="shared" si="26"/>
+        <v>1347914.23</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1674" s="4" t="s">
         <v>390</v>
       </c>
@@ -35851,8 +36761,15 @@
       <c r="D1674" s="3">
         <v>83950</v>
       </c>
-    </row>
-    <row r="1675" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1674" s="3">
+        <v>27.14</v>
+      </c>
+      <c r="F1674" s="3">
+        <f t="shared" si="26"/>
+        <v>2278403</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1675" s="4" t="s">
         <v>390</v>
       </c>
@@ -35865,8 +36782,15 @@
       <c r="D1675" s="3">
         <v>108071</v>
       </c>
-    </row>
-    <row r="1676" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1675" s="3">
+        <v>4.46</v>
+      </c>
+      <c r="F1675" s="3">
+        <f t="shared" si="26"/>
+        <v>481996.66</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1676" s="4" t="s">
         <v>390</v>
       </c>
@@ -35879,8 +36803,15 @@
       <c r="D1676" s="3">
         <v>86601</v>
       </c>
-    </row>
-    <row r="1677" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1676" s="3">
+        <v>8.2070000000000007</v>
+      </c>
+      <c r="F1676" s="3">
+        <f t="shared" si="26"/>
+        <v>710734.40700000001</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1677" s="4" t="s">
         <v>390</v>
       </c>
@@ -35893,8 +36824,15 @@
       <c r="D1677" s="3">
         <v>75683</v>
       </c>
-    </row>
-    <row r="1678" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1677" s="3">
+        <v>11.89</v>
+      </c>
+      <c r="F1677" s="3">
+        <f t="shared" si="26"/>
+        <v>899870.87</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1678" s="4" t="s">
         <v>390</v>
       </c>
@@ -35907,8 +36845,15 @@
       <c r="D1678" s="3">
         <v>3922</v>
       </c>
-    </row>
-    <row r="1679" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1678" s="3">
+        <v>39.4</v>
+      </c>
+      <c r="F1678" s="3">
+        <f t="shared" si="26"/>
+        <v>154526.79999999999</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1679" s="4" t="s">
         <v>390</v>
       </c>
@@ -35921,8 +36866,15 @@
       <c r="D1679" s="3">
         <v>7917</v>
       </c>
-    </row>
-    <row r="1680" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1679" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1679" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1680" s="4" t="s">
         <v>390</v>
       </c>
@@ -35935,8 +36887,15 @@
       <c r="D1680" s="3">
         <v>4360</v>
       </c>
-    </row>
-    <row r="1681" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1680" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1680" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1681" s="4" t="s">
         <v>390</v>
       </c>
@@ -35949,8 +36908,15 @@
       <c r="D1681" s="3">
         <v>5300</v>
       </c>
-    </row>
-    <row r="1682" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1681" s="3">
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="F1681" s="3">
+        <f t="shared" si="26"/>
+        <v>6757.4999999999991</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1682" s="4" t="s">
         <v>390</v>
       </c>
@@ -35963,8 +36929,15 @@
       <c r="D1682" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1683" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1682" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1682" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1683" s="4" t="s">
         <v>390</v>
       </c>
@@ -35977,8 +36950,15 @@
       <c r="D1683" s="3">
         <v>13333</v>
       </c>
-    </row>
-    <row r="1684" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1683" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1683" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1684" s="4" t="s">
         <v>390</v>
       </c>
@@ -35991,8 +36971,15 @@
       <c r="D1684" s="3">
         <v>5274</v>
       </c>
-    </row>
-    <row r="1685" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1684" s="3">
+        <v>61.072000000000003</v>
+      </c>
+      <c r="F1684" s="3">
+        <f t="shared" si="26"/>
+        <v>322093.728</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1685" s="4" t="s">
         <v>390</v>
       </c>
@@ -36005,8 +36992,15 @@
       <c r="D1685" s="3">
         <v>3726</v>
       </c>
-    </row>
-    <row r="1686" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1685" s="3">
+        <v>11</v>
+      </c>
+      <c r="F1685" s="3">
+        <f t="shared" si="26"/>
+        <v>40986</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1686" s="4" t="s">
         <v>390</v>
       </c>
@@ -36019,8 +37013,15 @@
       <c r="D1686" s="3">
         <v>5098</v>
       </c>
-    </row>
-    <row r="1687" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1686" s="3">
+        <v>1320</v>
+      </c>
+      <c r="F1686" s="3">
+        <f t="shared" si="26"/>
+        <v>6729360</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1687" s="4" t="s">
         <v>390</v>
       </c>
@@ -36033,8 +37034,15 @@
       <c r="D1687" s="3">
         <v>15784</v>
       </c>
-    </row>
-    <row r="1688" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1687" s="3">
+        <v>65</v>
+      </c>
+      <c r="F1687" s="3">
+        <f t="shared" si="26"/>
+        <v>1025960</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1688" s="4" t="s">
         <v>390</v>
       </c>
@@ -36047,8 +37055,15 @@
       <c r="D1688" s="3">
         <v>1765</v>
       </c>
-    </row>
-    <row r="1689" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1688" s="3">
+        <v>331.38</v>
+      </c>
+      <c r="F1688" s="3">
+        <f t="shared" si="26"/>
+        <v>584885.69999999995</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1689" s="4" t="s">
         <v>390</v>
       </c>
@@ -36061,8 +37076,15 @@
       <c r="D1689" s="3">
         <v>7176</v>
       </c>
-    </row>
-    <row r="1690" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1689" s="3">
+        <v>93.93</v>
+      </c>
+      <c r="F1689" s="3">
+        <f t="shared" si="26"/>
+        <v>674041.68</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1690" s="4" t="s">
         <v>390</v>
       </c>
@@ -36075,8 +37097,15 @@
       <c r="D1690" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1691" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1690" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1690" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1691" s="4" t="s">
         <v>390</v>
       </c>
@@ -36089,8 +37118,15 @@
       <c r="D1691" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1692" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1691" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1691" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1692" s="4" t="s">
         <v>390</v>
       </c>
@@ -36103,8 +37139,15 @@
       <c r="D1692" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1693" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1692" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1692" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1693" s="4" t="s">
         <v>390</v>
       </c>
@@ -36117,8 +37160,15 @@
       <c r="D1693" s="3">
         <v>4330</v>
       </c>
-    </row>
-    <row r="1694" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1693" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="F1693" s="3">
+        <f t="shared" si="26"/>
+        <v>10392</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1694" s="4" t="s">
         <v>390</v>
       </c>
@@ -36131,8 +37181,15 @@
       <c r="D1694" s="3">
         <v>13235</v>
       </c>
-    </row>
-    <row r="1695" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1694" s="3">
+        <v>74.400000000000006</v>
+      </c>
+      <c r="F1694" s="3">
+        <f t="shared" si="26"/>
+        <v>984684.00000000012</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1695" s="4" t="s">
         <v>390</v>
       </c>
@@ -36145,8 +37202,15 @@
       <c r="D1695" s="3">
         <v>15980</v>
       </c>
-    </row>
-    <row r="1696" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1695" s="3">
+        <v>298.5</v>
+      </c>
+      <c r="F1695" s="3">
+        <f t="shared" si="26"/>
+        <v>4770030</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1696" s="4" t="s">
         <v>390</v>
       </c>
@@ -36159,8 +37223,15 @@
       <c r="D1696" s="3">
         <v>18137</v>
       </c>
-    </row>
-    <row r="1697" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1696" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1696" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1697" s="4" t="s">
         <v>390</v>
       </c>
@@ -36173,8 +37244,15 @@
       <c r="D1697" s="3">
         <v>2300</v>
       </c>
-    </row>
-    <row r="1698" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1697" s="3">
+        <v>156.43</v>
+      </c>
+      <c r="F1697" s="3">
+        <f t="shared" si="26"/>
+        <v>359789</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1698" s="4" t="s">
         <v>390</v>
       </c>
@@ -36187,8 +37265,15 @@
       <c r="D1698" s="3">
         <v>5000</v>
       </c>
-    </row>
-    <row r="1699" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1698" s="3">
+        <v>53</v>
+      </c>
+      <c r="F1698" s="3">
+        <f t="shared" si="26"/>
+        <v>265000</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1699" s="4" t="s">
         <v>390</v>
       </c>
@@ -36201,8 +37286,15 @@
       <c r="D1699" s="3">
         <v>4043</v>
       </c>
-    </row>
-    <row r="1700" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1699" s="3">
+        <v>40</v>
+      </c>
+      <c r="F1699" s="3">
+        <f t="shared" si="26"/>
+        <v>161720</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1700" s="4" t="s">
         <v>390</v>
       </c>
@@ -36215,8 +37307,15 @@
       <c r="D1700" s="3">
         <v>12608</v>
       </c>
-    </row>
-    <row r="1701" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1700" s="3">
+        <v>13</v>
+      </c>
+      <c r="F1700" s="3">
+        <f t="shared" si="26"/>
+        <v>163904</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1701" s="4" t="s">
         <v>390</v>
       </c>
@@ -36229,8 +37328,15 @@
       <c r="D1701" s="3">
         <v>4472</v>
       </c>
-    </row>
-    <row r="1702" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1701" s="3">
+        <v>51.195</v>
+      </c>
+      <c r="F1701" s="3">
+        <f t="shared" si="26"/>
+        <v>228944.04</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1702" s="4" t="s">
         <v>390</v>
       </c>
@@ -36243,8 +37349,15 @@
       <c r="D1702" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1703" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1702" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1702" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1703" s="4" t="s">
         <v>390</v>
       </c>
@@ -36257,8 +37370,15 @@
       <c r="D1703" s="3">
         <v>58824</v>
       </c>
-    </row>
-    <row r="1704" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1703" s="3">
+        <v>0.215</v>
+      </c>
+      <c r="F1703" s="3">
+        <f t="shared" si="26"/>
+        <v>12647.16</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1704" s="4" t="s">
         <v>390</v>
       </c>
@@ -36271,8 +37391,15 @@
       <c r="D1704" s="3">
         <v>90684</v>
       </c>
-    </row>
-    <row r="1705" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1704" s="3">
+        <v>29</v>
+      </c>
+      <c r="F1704" s="3">
+        <f t="shared" si="26"/>
+        <v>2629836</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1705" s="4" t="s">
         <v>390</v>
       </c>
@@ -36285,8 +37412,15 @@
       <c r="D1705" s="3">
         <v>35853</v>
       </c>
-    </row>
-    <row r="1706" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1705" s="3">
+        <v>11.2</v>
+      </c>
+      <c r="F1705" s="3">
+        <f t="shared" si="26"/>
+        <v>401553.6</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1706" s="4" t="s">
         <v>390</v>
       </c>
@@ -36299,8 +37433,15 @@
       <c r="D1706" s="3">
         <v>8136</v>
       </c>
-    </row>
-    <row r="1707" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1706" s="3">
+        <v>129</v>
+      </c>
+      <c r="F1706" s="3">
+        <f t="shared" si="26"/>
+        <v>1049544</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1707" s="4" t="s">
         <v>390</v>
       </c>
@@ -36313,8 +37454,15 @@
       <c r="D1707" s="3">
         <v>3080</v>
       </c>
-    </row>
-    <row r="1708" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1707" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1707" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1708" s="4" t="s">
         <v>390</v>
       </c>
@@ -36327,8 +37475,15 @@
       <c r="D1708" s="3">
         <v>2157</v>
       </c>
-    </row>
-    <row r="1709" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1708" s="3">
+        <v>2.7949999999999999</v>
+      </c>
+      <c r="F1708" s="3">
+        <f t="shared" si="26"/>
+        <v>6028.8149999999996</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1709" s="4" t="s">
         <v>390</v>
       </c>
@@ -36341,8 +37496,15 @@
       <c r="D1709" s="3">
         <v>4412</v>
       </c>
-    </row>
-    <row r="1710" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1709" s="3">
+        <v>1160</v>
+      </c>
+      <c r="F1709" s="3">
+        <f t="shared" si="26"/>
+        <v>5117920</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1710" s="4" t="s">
         <v>390</v>
       </c>
@@ -36355,8 +37517,15 @@
       <c r="D1710" s="3">
         <v>4902</v>
       </c>
-    </row>
-    <row r="1711" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1710" s="3">
+        <v>1668</v>
+      </c>
+      <c r="F1710" s="3">
+        <f t="shared" si="26"/>
+        <v>8176536</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1711" s="4" t="s">
         <v>390</v>
       </c>
@@ -36369,8 +37538,15 @@
       <c r="D1711" s="3">
         <v>9500</v>
       </c>
-    </row>
-    <row r="1712" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1711" s="3">
+        <v>60</v>
+      </c>
+      <c r="F1711" s="3">
+        <f t="shared" si="26"/>
+        <v>570000</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1712" s="4" t="s">
         <v>390</v>
       </c>
@@ -36383,8 +37559,15 @@
       <c r="D1712" s="3">
         <v>10670</v>
       </c>
-    </row>
-    <row r="1713" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1712" s="3">
+        <v>100</v>
+      </c>
+      <c r="F1712" s="3">
+        <f t="shared" si="26"/>
+        <v>1067000</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1713" s="4" t="s">
         <v>390</v>
       </c>
@@ -36397,8 +37580,15 @@
       <c r="D1713" s="3">
         <v>12720</v>
       </c>
-    </row>
-    <row r="1714" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1713" s="3">
+        <v>259.89999999999998</v>
+      </c>
+      <c r="F1713" s="3">
+        <f t="shared" si="26"/>
+        <v>3305927.9999999995</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1714" s="4" t="s">
         <v>390</v>
       </c>
@@ -36411,8 +37601,15 @@
       <c r="D1714" s="3">
         <v>2069</v>
       </c>
-    </row>
-    <row r="1715" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1714" s="3">
+        <v>98.4</v>
+      </c>
+      <c r="F1714" s="3">
+        <f t="shared" si="26"/>
+        <v>203589.6</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1715" s="4" t="s">
         <v>390</v>
       </c>
@@ -36425,8 +37622,15 @@
       <c r="D1715" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1716" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1715" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1715" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1716" s="4" t="s">
         <v>390</v>
       </c>
@@ -36439,8 +37643,15 @@
       <c r="D1716" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1717" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1716" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1716" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1717" s="4" t="s">
         <v>390</v>
       </c>
@@ -36453,8 +37664,15 @@
       <c r="D1717" s="3">
         <v>18700</v>
       </c>
-    </row>
-    <row r="1718" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1717" s="3">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F1717" s="3">
+        <f t="shared" si="26"/>
+        <v>2618.0000000000005</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1718" s="4" t="s">
         <v>390</v>
       </c>
@@ -36467,8 +37685,15 @@
       <c r="D1718" s="3">
         <v>34000</v>
       </c>
-    </row>
-    <row r="1719" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1718" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F1718" s="3">
+        <f t="shared" si="26"/>
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1719" s="4" t="s">
         <v>390</v>
       </c>
@@ -36481,8 +37706,15 @@
       <c r="D1719" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="1720" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1719" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="F1719" s="3">
+        <f t="shared" si="26"/>
+        <v>12480</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1720" s="4" t="s">
         <v>390</v>
       </c>
@@ -36495,8 +37727,15 @@
       <c r="D1720" s="3">
         <v>7733</v>
       </c>
-    </row>
-    <row r="1721" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1720" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1720" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1721" s="4" t="s">
         <v>390</v>
       </c>
@@ -36509,8 +37748,15 @@
       <c r="D1721" s="3">
         <v>1804</v>
       </c>
-    </row>
-    <row r="1722" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1721" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1721" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1722" s="4" t="s">
         <v>390</v>
       </c>
@@ -36523,8 +37769,15 @@
       <c r="D1722" s="3">
         <v>4060</v>
       </c>
-    </row>
-    <row r="1723" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1722" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1722" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1723" s="4" t="s">
         <v>390</v>
       </c>
@@ -36537,8 +37790,15 @@
       <c r="D1723" s="3">
         <v>1967</v>
       </c>
-    </row>
-    <row r="1724" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1723" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1723" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1724" s="4" t="s">
         <v>390</v>
       </c>
@@ -36551,8 +37811,15 @@
       <c r="D1724" s="3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="1725" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1724" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1724" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1725" s="4" t="s">
         <v>390</v>
       </c>
@@ -36565,8 +37832,15 @@
       <c r="D1725" s="3">
         <v>3402</v>
       </c>
-    </row>
-    <row r="1726" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1725" s="3">
+        <v>173.08</v>
+      </c>
+      <c r="F1725" s="3">
+        <f t="shared" si="26"/>
+        <v>588818.16</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1726" s="4" t="s">
         <v>390</v>
       </c>
@@ -36579,8 +37853,15 @@
       <c r="D1726" s="3">
         <v>6843</v>
       </c>
-    </row>
-    <row r="1727" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1726" s="3">
+        <v>19</v>
+      </c>
+      <c r="F1726" s="3">
+        <f t="shared" si="26"/>
+        <v>130017</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1727" s="4" t="s">
         <v>390</v>
       </c>
@@ -36593,8 +37874,15 @@
       <c r="D1727" s="3">
         <v>6000</v>
       </c>
-    </row>
-    <row r="1728" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1727" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="F1727" s="3">
+        <f t="shared" si="26"/>
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1728" s="4" t="s">
         <v>390</v>
       </c>
@@ -36607,8 +37895,15 @@
       <c r="D1728" s="3">
         <v>5265</v>
       </c>
-    </row>
-    <row r="1729" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1728" s="3">
+        <v>39</v>
+      </c>
+      <c r="F1728" s="3">
+        <f t="shared" si="26"/>
+        <v>205335</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1729" s="4" t="s">
         <v>390</v>
       </c>
@@ -36621,8 +37916,15 @@
       <c r="D1729" s="3">
         <v>6863</v>
       </c>
-    </row>
-    <row r="1730" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1729" s="3">
+        <v>120</v>
+      </c>
+      <c r="F1729" s="3">
+        <f t="shared" si="26"/>
+        <v>823560</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1730" s="4" t="s">
         <v>390</v>
       </c>
@@ -36635,8 +37937,15 @@
       <c r="D1730" s="3">
         <v>23800</v>
       </c>
-    </row>
-    <row r="1731" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1730" s="3">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="F1730" s="3">
+        <f t="shared" si="26"/>
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1731" s="4" t="s">
         <v>390</v>
       </c>
@@ -36649,8 +37958,15 @@
       <c r="D1731" s="3">
         <v>13330</v>
       </c>
-    </row>
-    <row r="1732" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1731" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1731" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1732" s="4" t="s">
         <v>390</v>
       </c>
@@ -36663,8 +37979,15 @@
       <c r="D1732" s="3">
         <v>4062</v>
       </c>
-    </row>
-    <row r="1733" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1732" s="3">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="F1732" s="3">
+        <f t="shared" si="26"/>
+        <v>710.84999999999991</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1733" s="4" t="s">
         <v>390</v>
       </c>
@@ -36677,8 +38000,15 @@
       <c r="D1733" s="3">
         <v>39000</v>
       </c>
-    </row>
-    <row r="1734" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1733" s="3">
+        <v>0.74</v>
+      </c>
+      <c r="F1733" s="3">
+        <f t="shared" si="26"/>
+        <v>28860</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1734" s="4" t="s">
         <v>390</v>
       </c>
@@ -36691,8 +38021,15 @@
       <c r="D1734" s="3">
         <v>11500</v>
       </c>
-    </row>
-    <row r="1735" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1734" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1734" s="3">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1735" s="4" t="s">
         <v>390</v>
       </c>
@@ -36705,8 +38042,15 @@
       <c r="D1735" s="3">
         <v>3444</v>
       </c>
-    </row>
-    <row r="1736" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1735" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1735" s="3">
+        <f t="shared" ref="F1735:F1798" si="27">E1735*D1735</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1736" s="4" t="s">
         <v>390</v>
       </c>
@@ -36719,8 +38063,15 @@
       <c r="D1736" s="3">
         <v>15530</v>
       </c>
-    </row>
-    <row r="1737" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1736" s="3">
+        <v>20</v>
+      </c>
+      <c r="F1736" s="3">
+        <f t="shared" si="27"/>
+        <v>310600</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1737" s="4" t="s">
         <v>390</v>
       </c>
@@ -36733,8 +38084,15 @@
       <c r="D1737" s="3">
         <v>11670</v>
       </c>
-    </row>
-    <row r="1738" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1737" s="3">
+        <v>40</v>
+      </c>
+      <c r="F1737" s="3">
+        <f t="shared" si="27"/>
+        <v>466800</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1738" s="4" t="s">
         <v>390</v>
       </c>
@@ -36747,8 +38105,15 @@
       <c r="D1738" s="3">
         <v>11940</v>
       </c>
-    </row>
-    <row r="1739" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1738" s="3">
+        <v>20</v>
+      </c>
+      <c r="F1738" s="3">
+        <f t="shared" si="27"/>
+        <v>238800</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1739" s="4" t="s">
         <v>390</v>
       </c>
@@ -36761,8 +38126,15 @@
       <c r="D1739" s="3">
         <v>6226</v>
       </c>
-    </row>
-    <row r="1740" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1739" s="3">
+        <v>65</v>
+      </c>
+      <c r="F1739" s="3">
+        <f t="shared" si="27"/>
+        <v>404690</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1740" s="4" t="s">
         <v>390</v>
       </c>
@@ -36775,8 +38147,15 @@
       <c r="D1740" s="3">
         <v>2098</v>
       </c>
-    </row>
-    <row r="1741" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1740" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1740" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1741" s="4" t="s">
         <v>390</v>
       </c>
@@ -36789,8 +38168,15 @@
       <c r="D1741" s="3">
         <v>5800</v>
       </c>
-    </row>
-    <row r="1742" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1741" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1741" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1742" s="4" t="s">
         <v>390</v>
       </c>
@@ -36803,8 +38189,15 @@
       <c r="D1742" s="3">
         <v>27667</v>
       </c>
-    </row>
-    <row r="1743" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1742" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1742" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1743" s="4" t="s">
         <v>390</v>
       </c>
@@ -36817,8 +38210,15 @@
       <c r="D1743" s="3">
         <v>3441</v>
       </c>
-    </row>
-    <row r="1744" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1743" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1743" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1744" s="4" t="s">
         <v>390</v>
       </c>
@@ -36831,8 +38231,15 @@
       <c r="D1744" s="3">
         <v>8920</v>
       </c>
-    </row>
-    <row r="1745" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1744" s="3">
+        <v>20</v>
+      </c>
+      <c r="F1744" s="3">
+        <f t="shared" si="27"/>
+        <v>178400</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1745" s="4" t="s">
         <v>390</v>
       </c>
@@ -36845,8 +38252,15 @@
       <c r="D1745" s="3">
         <v>10520</v>
       </c>
-    </row>
-    <row r="1746" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1745" s="3">
+        <v>100</v>
+      </c>
+      <c r="F1745" s="3">
+        <f t="shared" si="27"/>
+        <v>1052000</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1746" s="4" t="s">
         <v>390</v>
       </c>
@@ -36859,8 +38273,15 @@
       <c r="D1746" s="3">
         <v>10550</v>
       </c>
-    </row>
-    <row r="1747" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1746" s="3">
+        <v>40</v>
+      </c>
+      <c r="F1746" s="3">
+        <f t="shared" si="27"/>
+        <v>422000</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1747" s="4" t="s">
         <v>390</v>
       </c>
@@ -36873,8 +38294,15 @@
       <c r="D1747" s="3">
         <v>11060</v>
       </c>
-    </row>
-    <row r="1748" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1747" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1747" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1748" s="4" t="s">
         <v>390</v>
       </c>
@@ -36887,8 +38315,15 @@
       <c r="D1748" s="3">
         <v>12760</v>
       </c>
-    </row>
-    <row r="1749" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1748" s="3">
+        <v>120</v>
+      </c>
+      <c r="F1748" s="3">
+        <f t="shared" si="27"/>
+        <v>1531200</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1749" s="4" t="s">
         <v>390</v>
       </c>
@@ -36901,8 +38336,15 @@
       <c r="D1749" s="3">
         <v>13200</v>
       </c>
-    </row>
-    <row r="1750" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1749" s="3">
+        <v>20</v>
+      </c>
+      <c r="F1749" s="3">
+        <f t="shared" si="27"/>
+        <v>264000</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1750" s="4" t="s">
         <v>390</v>
       </c>
@@ -36915,8 +38357,15 @@
       <c r="D1750" s="3">
         <v>10720</v>
       </c>
-    </row>
-    <row r="1751" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1750" s="3">
+        <v>20</v>
+      </c>
+      <c r="F1750" s="3">
+        <f t="shared" si="27"/>
+        <v>214400</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1751" s="4" t="s">
         <v>390</v>
       </c>
@@ -36929,8 +38378,15 @@
       <c r="D1751" s="3">
         <v>12720</v>
       </c>
-    </row>
-    <row r="1752" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1751" s="3">
+        <v>10</v>
+      </c>
+      <c r="F1751" s="3">
+        <f t="shared" si="27"/>
+        <v>127200</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1752" s="4" t="s">
         <v>390</v>
       </c>
@@ -36943,8 +38399,15 @@
       <c r="D1752" s="3">
         <v>14000</v>
       </c>
-    </row>
-    <row r="1753" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1752" s="3">
+        <v>10</v>
+      </c>
+      <c r="F1752" s="3">
+        <f t="shared" si="27"/>
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1753" s="4" t="s">
         <v>390</v>
       </c>
@@ -36957,8 +38420,15 @@
       <c r="D1753" s="3">
         <v>1618</v>
       </c>
-    </row>
-    <row r="1754" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1753" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1753" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1754" s="4" t="s">
         <v>390</v>
       </c>
@@ -36971,8 +38441,15 @@
       <c r="D1754" s="3">
         <v>12190</v>
       </c>
-    </row>
-    <row r="1755" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1754" s="3">
+        <v>220</v>
+      </c>
+      <c r="F1754" s="3">
+        <f t="shared" si="27"/>
+        <v>2681800</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1755" s="4" t="s">
         <v>390</v>
       </c>
@@ -36985,8 +38462,15 @@
       <c r="D1755" s="3">
         <v>10180</v>
       </c>
-    </row>
-    <row r="1756" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1755" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1755" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1756" s="4" t="s">
         <v>390</v>
       </c>
@@ -36999,8 +38483,15 @@
       <c r="D1756" s="3">
         <v>9020</v>
       </c>
-    </row>
-    <row r="1757" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1756" s="3">
+        <v>146</v>
+      </c>
+      <c r="F1756" s="3">
+        <f t="shared" si="27"/>
+        <v>1316920</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1757" s="4" t="s">
         <v>390</v>
       </c>
@@ -37013,8 +38504,15 @@
       <c r="D1757" s="3">
         <v>2693</v>
       </c>
-    </row>
-    <row r="1758" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1757" s="3">
+        <v>130</v>
+      </c>
+      <c r="F1757" s="3">
+        <f t="shared" si="27"/>
+        <v>350090</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1758" s="4" t="s">
         <v>390</v>
       </c>
@@ -37027,8 +38525,15 @@
       <c r="D1758" s="3">
         <v>2591</v>
       </c>
-    </row>
-    <row r="1759" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1758" s="3">
+        <v>130</v>
+      </c>
+      <c r="F1758" s="3">
+        <f t="shared" si="27"/>
+        <v>336830</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1759" s="4" t="s">
         <v>390</v>
       </c>
@@ -37041,8 +38546,15 @@
       <c r="D1759" s="3">
         <v>4706</v>
       </c>
-    </row>
-    <row r="1760" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1759" s="3">
+        <v>121</v>
+      </c>
+      <c r="F1759" s="3">
+        <f t="shared" si="27"/>
+        <v>569426</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1760" s="4" t="s">
         <v>390</v>
       </c>
@@ -37055,8 +38567,15 @@
       <c r="D1760" s="3">
         <v>3922</v>
       </c>
-    </row>
-    <row r="1761" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1760" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1760" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1761" s="4" t="s">
         <v>390</v>
       </c>
@@ -37069,8 +38588,15 @@
       <c r="D1761" s="3">
         <v>8333</v>
       </c>
-    </row>
-    <row r="1762" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1761" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1761" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1762" s="4" t="s">
         <v>390</v>
       </c>
@@ -37083,8 +38609,15 @@
       <c r="D1762" s="3">
         <v>6435</v>
       </c>
-    </row>
-    <row r="1763" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1762" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1762" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1763" s="4" t="s">
         <v>390</v>
       </c>
@@ -37097,8 +38630,15 @@
       <c r="D1763" s="3">
         <v>8720</v>
       </c>
-    </row>
-    <row r="1764" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1763" s="3">
+        <v>21.4</v>
+      </c>
+      <c r="F1763" s="3">
+        <f t="shared" si="27"/>
+        <v>186608</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1764" s="4" t="s">
         <v>390</v>
       </c>
@@ -37111,8 +38651,15 @@
       <c r="D1764" s="3">
         <v>2637</v>
       </c>
-    </row>
-    <row r="1765" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1764" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1764" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1765" s="4" t="s">
         <v>390</v>
       </c>
@@ -37125,8 +38672,15 @@
       <c r="D1765" s="3">
         <v>4890</v>
       </c>
-    </row>
-    <row r="1766" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1765" s="3">
+        <v>390</v>
+      </c>
+      <c r="F1765" s="3">
+        <f t="shared" si="27"/>
+        <v>1907100</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1766" s="4" t="s">
         <v>390</v>
       </c>
@@ -37139,8 +38693,15 @@
       <c r="D1766" s="3">
         <v>15500</v>
       </c>
-    </row>
-    <row r="1767" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1766" s="3">
+        <v>126</v>
+      </c>
+      <c r="F1766" s="3">
+        <f t="shared" si="27"/>
+        <v>1953000</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1767" s="4" t="s">
         <v>390</v>
       </c>
@@ -37153,8 +38714,15 @@
       <c r="D1767" s="3">
         <v>18500</v>
       </c>
-    </row>
-    <row r="1768" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1767" s="3">
+        <v>150</v>
+      </c>
+      <c r="F1767" s="3">
+        <f t="shared" si="27"/>
+        <v>2775000</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1768" s="4" t="s">
         <v>390</v>
       </c>
@@ -37167,8 +38735,15 @@
       <c r="D1768" s="3">
         <v>32843</v>
       </c>
-    </row>
-    <row r="1769" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1768" s="3">
+        <v>45</v>
+      </c>
+      <c r="F1768" s="3">
+        <f t="shared" si="27"/>
+        <v>1477935</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1769" s="4" t="s">
         <v>390</v>
       </c>
@@ -37181,8 +38756,15 @@
       <c r="D1769" s="3">
         <v>18353</v>
       </c>
-    </row>
-    <row r="1770" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1769" s="3">
+        <v>13.2</v>
+      </c>
+      <c r="F1769" s="3">
+        <f t="shared" si="27"/>
+        <v>242259.59999999998</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1770" s="4" t="s">
         <v>390</v>
       </c>
@@ -37195,8 +38777,15 @@
       <c r="D1770" s="3">
         <v>1657</v>
       </c>
-    </row>
-    <row r="1771" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1770" s="3">
+        <v>100</v>
+      </c>
+      <c r="F1770" s="3">
+        <f t="shared" si="27"/>
+        <v>165700</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1771" s="4" t="s">
         <v>390</v>
       </c>
@@ -37209,8 +38798,15 @@
       <c r="D1771" s="3">
         <v>12430</v>
       </c>
-    </row>
-    <row r="1772" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1771" s="3">
+        <v>1.23</v>
+      </c>
+      <c r="F1771" s="3">
+        <f t="shared" si="27"/>
+        <v>15288.9</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1772" s="4" t="s">
         <v>390</v>
       </c>
@@ -37223,8 +38819,15 @@
       <c r="D1772" s="3">
         <v>14020</v>
       </c>
-    </row>
-    <row r="1773" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1772" s="3">
+        <v>260</v>
+      </c>
+      <c r="F1772" s="3">
+        <f t="shared" si="27"/>
+        <v>3645200</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1773" s="4" t="s">
         <v>390</v>
       </c>
@@ -37237,8 +38840,15 @@
       <c r="D1773" s="3">
         <v>4500</v>
       </c>
-    </row>
-    <row r="1774" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1773" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1773" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1774" s="4" t="s">
         <v>390</v>
       </c>
@@ -37251,8 +38861,15 @@
       <c r="D1774" s="3">
         <v>24510</v>
       </c>
-    </row>
-    <row r="1775" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1774" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1774" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1775" s="4" t="s">
         <v>390</v>
       </c>
@@ -37265,8 +38882,15 @@
       <c r="D1775" s="3">
         <v>19608</v>
       </c>
-    </row>
-    <row r="1776" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1775" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1775" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1776" s="4" t="s">
         <v>390</v>
       </c>
@@ -37279,8 +38903,15 @@
       <c r="D1776" s="3">
         <v>19608</v>
       </c>
-    </row>
-    <row r="1777" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1776" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1776" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1777" s="4" t="s">
         <v>390</v>
       </c>
@@ -37293,8 +38924,15 @@
       <c r="D1777" s="3">
         <v>9833</v>
       </c>
-    </row>
-    <row r="1778" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1777" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1777" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1778" s="4" t="s">
         <v>390</v>
       </c>
@@ -37307,8 +38945,15 @@
       <c r="D1778" s="3">
         <v>4220</v>
       </c>
-    </row>
-    <row r="1779" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1778" s="3">
+        <v>12</v>
+      </c>
+      <c r="F1778" s="3">
+        <f t="shared" si="27"/>
+        <v>50640</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1779" s="4" t="s">
         <v>390</v>
       </c>
@@ -37321,8 +38966,15 @@
       <c r="D1779" s="3">
         <v>7647</v>
       </c>
-    </row>
-    <row r="1780" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1779" s="3">
+        <v>40</v>
+      </c>
+      <c r="F1779" s="3">
+        <f t="shared" si="27"/>
+        <v>305880</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1780" s="4" t="s">
         <v>390</v>
       </c>
@@ -37335,8 +38987,15 @@
       <c r="D1780" s="3">
         <v>40196</v>
       </c>
-    </row>
-    <row r="1781" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1780" s="3">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="F1780" s="3">
+        <f t="shared" si="27"/>
+        <v>7034.2999999999993</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1781" s="4" t="s">
         <v>390</v>
       </c>
@@ -37349,8 +39008,15 @@
       <c r="D1781" s="3">
         <v>9000</v>
       </c>
-    </row>
-    <row r="1782" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1781" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1781" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1782" s="4" t="s">
         <v>390</v>
       </c>
@@ -37363,8 +39029,15 @@
       <c r="D1782" s="3">
         <v>25820</v>
       </c>
-    </row>
-    <row r="1783" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1782" s="3">
+        <v>4</v>
+      </c>
+      <c r="F1782" s="3">
+        <f t="shared" si="27"/>
+        <v>103280</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1783" s="4" t="s">
         <v>390</v>
       </c>
@@ -37377,8 +39050,15 @@
       <c r="D1783" s="3">
         <v>10588</v>
       </c>
-    </row>
-    <row r="1784" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1783" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1783" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1784" s="4" t="s">
         <v>390</v>
       </c>
@@ -37391,8 +39071,15 @@
       <c r="D1784" s="3">
         <v>14020</v>
       </c>
-    </row>
-    <row r="1785" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1784" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1784" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1785" s="4" t="s">
         <v>390</v>
       </c>
@@ -37405,8 +39092,15 @@
       <c r="D1785" s="3">
         <v>9020</v>
       </c>
-    </row>
-    <row r="1786" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1785" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1785" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1786" s="4" t="s">
         <v>390</v>
       </c>
@@ -37419,8 +39113,15 @@
       <c r="D1786" s="3">
         <v>9520</v>
       </c>
-    </row>
-    <row r="1787" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1786" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1786" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1787" s="4" t="s">
         <v>390</v>
       </c>
@@ -37433,8 +39134,15 @@
       <c r="D1787" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1788" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1787" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1787" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1788" s="4" t="s">
         <v>390</v>
       </c>
@@ -37447,8 +39155,15 @@
       <c r="D1788" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1789" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1788" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1788" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1789" s="4" t="s">
         <v>390</v>
       </c>
@@ -37461,8 +39176,15 @@
       <c r="D1789" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1790" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1789" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1789" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1790" s="4" t="s">
         <v>390</v>
       </c>
@@ -37475,8 +39197,15 @@
       <c r="D1790" s="3">
         <v>10000</v>
       </c>
-    </row>
-    <row r="1791" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1790" s="3">
+        <v>110</v>
+      </c>
+      <c r="F1790" s="3">
+        <f t="shared" si="27"/>
+        <v>1100000</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1791" s="4" t="s">
         <v>390</v>
       </c>
@@ -37489,8 +39218,15 @@
       <c r="D1791" s="3">
         <v>10230</v>
       </c>
-    </row>
-    <row r="1792" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1791" s="3">
+        <v>557</v>
+      </c>
+      <c r="F1791" s="3">
+        <f t="shared" si="27"/>
+        <v>5698110</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1792" s="4" t="s">
         <v>390</v>
       </c>
@@ -37503,8 +39239,15 @@
       <c r="D1792" s="3">
         <v>11800</v>
       </c>
-    </row>
-    <row r="1793" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1792" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1792" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1793" s="4" t="s">
         <v>390</v>
       </c>
@@ -37517,8 +39260,15 @@
       <c r="D1793" s="3">
         <v>6863</v>
       </c>
-    </row>
-    <row r="1794" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1793" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1793" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1794" s="4" t="s">
         <v>390</v>
       </c>
@@ -37531,8 +39281,15 @@
       <c r="D1794" s="3">
         <v>13235</v>
       </c>
-    </row>
-    <row r="1795" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1794" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1794" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1795" s="4" t="s">
         <v>390</v>
       </c>
@@ -37545,8 +39302,15 @@
       <c r="D1795" s="3">
         <v>8235</v>
       </c>
-    </row>
-    <row r="1796" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1795" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1795" s="3">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1796" s="4" t="s">
         <v>390</v>
       </c>
@@ -37559,8 +39323,15 @@
       <c r="D1796" s="3">
         <v>49100</v>
       </c>
-    </row>
-    <row r="1797" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1796" s="3">
+        <v>40.96</v>
+      </c>
+      <c r="F1796" s="3">
+        <f t="shared" si="27"/>
+        <v>2011136</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1797" s="4" t="s">
         <v>390</v>
       </c>
@@ -37573,8 +39344,15 @@
       <c r="D1797" s="3">
         <v>70000</v>
       </c>
-    </row>
-    <row r="1798" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1797" s="3">
+        <v>39.35</v>
+      </c>
+      <c r="F1797" s="3">
+        <f t="shared" si="27"/>
+        <v>2754500</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1798" s="4" t="s">
         <v>390</v>
       </c>
@@ -37587,8 +39365,15 @@
       <c r="D1798" s="3">
         <v>66700</v>
       </c>
-    </row>
-    <row r="1799" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1798" s="3">
+        <v>94.27</v>
+      </c>
+      <c r="F1798" s="3">
+        <f t="shared" si="27"/>
+        <v>6287809</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1799" s="4" t="s">
         <v>390</v>
       </c>
@@ -37601,8 +39386,15 @@
       <c r="D1799" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="1800" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1799" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1799" s="3">
+        <f t="shared" ref="F1799:F1800" si="28">E1799*D1799</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1800" s="4" t="s">
         <v>390</v>
       </c>
@@ -37613,6 +39405,13 @@
         <v>384</v>
       </c>
       <c r="D1800" s="3">
+        <v>0</v>
+      </c>
+      <c r="E1800" s="3">
+        <v>0</v>
+      </c>
+      <c r="F1800" s="3">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
